--- a/templates/stock_template.xlsx
+++ b/templates/stock_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nan2.shao\Desktop\Inventory\0814\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18464B30-B8CB-401B-9322-188AAC0C5D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B75A69-24E1-4239-8D5C-1FCD31B8CE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="752" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14105" uniqueCount="3073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14105" uniqueCount="3072">
   <si>
     <t>SKU no.</t>
   </si>
@@ -9249,10 +9249,6 @@
   </si>
   <si>
     <t>TCL-MG715DT210-68NS</t>
-  </si>
-  <si>
-    <t>Reserve</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>S-Class-68</t>
@@ -9444,7 +9440,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A1:Q1074" totalsRowShown="0">
-  <autoFilter ref="A1:Q1074" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:Q1074" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Cells"/>
+        <filter val="Drive"/>
+        <filter val="Heat Pump"/>
+        <filter val="MI"/>
+        <filter val="Non-PV"/>
+        <filter val="Reserve"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU no."/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Ordered Item"/>
@@ -9849,7 +9856,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3060</v>
       </c>
@@ -9890,7 +9897,7 @@
         <v>445</v>
       </c>
       <c r="O2" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="P2" t="s">
         <v>2710</v>
@@ -9907,7 +9914,7 @@
         <v>3066</v>
       </c>
       <c r="D3" t="s">
-        <v>3068</v>
+        <v>2637</v>
       </c>
       <c r="E3" t="s">
         <v>2637</v>
@@ -9916,7 +9923,7 @@
         <v>2566</v>
       </c>
       <c r="G3" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="J3" t="s">
         <v>2668</v>
@@ -9945,10 +9952,10 @@
         <v>3062</v>
       </c>
       <c r="C4" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="D4" t="s">
-        <v>3068</v>
+        <v>2637</v>
       </c>
       <c r="E4" t="s">
         <v>2637</v>
@@ -9957,7 +9964,7 @@
         <v>2566</v>
       </c>
       <c r="G4" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="J4" t="s">
         <v>2668</v>
@@ -9972,7 +9979,7 @@
         <v>3062</v>
       </c>
       <c r="O4" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="P4" t="s">
         <v>2566</v>
@@ -9981,7 +9988,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3063</v>
       </c>
@@ -9992,7 +9999,7 @@
         <v>2709</v>
       </c>
       <c r="E5" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -10022,16 +10029,16 @@
         <v>715</v>
       </c>
       <c r="O5" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="P5" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="Q5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3064</v>
       </c>
@@ -10072,7 +10079,7 @@
         <v>720</v>
       </c>
       <c r="O6" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="P6" t="s">
         <v>2988</v>
@@ -10081,7 +10088,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" ht="15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>3056</v>
       </c>
@@ -10131,7 +10138,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -10178,7 +10185,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -10228,7 +10235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -10278,7 +10285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -10328,7 +10335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -10378,7 +10385,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -11659,7 +11666,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -11712,7 +11719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -11765,7 +11772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -11818,7 +11825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -11871,7 +11878,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -11924,7 +11931,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>133</v>
       </c>
@@ -11977,7 +11984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -12027,7 +12034,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>140</v>
       </c>
@@ -12077,7 +12084,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>143</v>
       </c>
@@ -12127,7 +12134,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>146</v>
       </c>
@@ -12177,7 +12184,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>149</v>
       </c>
@@ -12227,7 +12234,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>153</v>
       </c>
@@ -12277,7 +12284,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>155</v>
       </c>
@@ -12327,7 +12334,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>156</v>
       </c>
@@ -12377,7 +12384,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>158</v>
       </c>
@@ -12427,7 +12434,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>159</v>
       </c>
@@ -12477,7 +12484,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>160</v>
       </c>
@@ -12527,7 +12534,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>161</v>
       </c>
@@ -12577,7 +12584,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>162</v>
       </c>
@@ -12627,7 +12634,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>165</v>
       </c>
@@ -12680,7 +12687,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>169</v>
       </c>
@@ -12733,7 +12740,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>172</v>
       </c>
@@ -12786,7 +12793,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>175</v>
       </c>
@@ -12839,7 +12846,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -12892,7 +12899,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>181</v>
       </c>
@@ -12945,7 +12952,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>184</v>
       </c>
@@ -12998,7 +13005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>187</v>
       </c>
@@ -13051,7 +13058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>190</v>
       </c>
@@ -13548,7 +13555,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>221</v>
       </c>
@@ -13598,7 +13605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>229</v>
       </c>
@@ -13648,7 +13655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>233</v>
       </c>
@@ -13698,7 +13705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>236</v>
       </c>
@@ -13748,7 +13755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>240</v>
       </c>
@@ -13798,7 +13805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>243</v>
       </c>
@@ -13848,7 +13855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>247</v>
       </c>
@@ -13898,7 +13905,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>250</v>
       </c>
@@ -13948,7 +13955,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>254</v>
       </c>
@@ -13998,7 +14005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>257</v>
       </c>
@@ -14048,7 +14055,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>261</v>
       </c>
@@ -14098,7 +14105,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>266</v>
       </c>
@@ -14148,7 +14155,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>270</v>
       </c>
@@ -14198,7 +14205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>273</v>
       </c>
@@ -14248,7 +14255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>275</v>
       </c>
@@ -14298,7 +14305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>278</v>
       </c>
@@ -14348,7 +14355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>281</v>
       </c>
@@ -14398,7 +14405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>284</v>
       </c>
@@ -14448,7 +14455,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>287</v>
       </c>
@@ -14498,7 +14505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>289</v>
       </c>
@@ -14548,7 +14555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>292</v>
       </c>
@@ -14592,7 +14599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>294</v>
       </c>
@@ -14642,7 +14649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>298</v>
       </c>
@@ -14692,7 +14699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>302</v>
       </c>
@@ -14742,7 +14749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>306</v>
       </c>
@@ -14792,7 +14799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>309</v>
       </c>
@@ -14842,7 +14849,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>311</v>
       </c>
@@ -14892,7 +14899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>313</v>
       </c>
@@ -14942,7 +14949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>315</v>
       </c>
@@ -14992,7 +14999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>318</v>
       </c>
@@ -15042,7 +15049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>321</v>
       </c>
@@ -15092,7 +15099,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>324</v>
       </c>
@@ -15142,7 +15149,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>326</v>
       </c>
@@ -15192,7 +15199,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>329</v>
       </c>
@@ -15242,7 +15249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>332</v>
       </c>
@@ -15292,7 +15299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>335</v>
       </c>
@@ -15342,7 +15349,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>339</v>
       </c>
@@ -15392,7 +15399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>341</v>
       </c>
@@ -15442,7 +15449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>344</v>
       </c>
@@ -15492,7 +15499,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>347</v>
       </c>
@@ -15542,7 +15549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>349</v>
       </c>
@@ -15592,7 +15599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>352</v>
       </c>
@@ -15642,7 +15649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>356</v>
       </c>
@@ -15692,7 +15699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>358</v>
       </c>
@@ -15742,7 +15749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>361</v>
       </c>
@@ -15792,7 +15799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>363</v>
       </c>
@@ -15842,7 +15849,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>366</v>
       </c>
@@ -15892,7 +15899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>369</v>
       </c>
@@ -15942,7 +15949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>373</v>
       </c>
@@ -15992,7 +15999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>375</v>
       </c>
@@ -16042,7 +16049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>378</v>
       </c>
@@ -16092,7 +16099,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>381</v>
       </c>
@@ -16142,7 +16149,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>383</v>
       </c>
@@ -16192,7 +16199,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>386</v>
       </c>
@@ -16242,7 +16249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>390</v>
       </c>
@@ -16292,7 +16299,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>392</v>
       </c>
@@ -16342,7 +16349,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>395</v>
       </c>
@@ -16392,7 +16399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>397</v>
       </c>
@@ -16442,7 +16449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>400</v>
       </c>
@@ -16492,7 +16499,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>402</v>
       </c>
@@ -16542,7 +16549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>405</v>
       </c>
@@ -16589,7 +16596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>407</v>
       </c>
@@ -16639,7 +16646,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>414</v>
       </c>
@@ -16689,7 +16696,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>416</v>
       </c>
@@ -16739,7 +16746,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>418</v>
       </c>
@@ -16789,7 +16796,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>421</v>
       </c>
@@ -16839,7 +16846,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>424</v>
       </c>
@@ -16889,7 +16896,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>428</v>
       </c>
@@ -16939,7 +16946,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>430</v>
       </c>
@@ -16989,7 +16996,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>434</v>
       </c>
@@ -17039,7 +17046,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>438</v>
       </c>
@@ -17089,7 +17096,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>441</v>
       </c>
@@ -17139,7 +17146,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>443</v>
       </c>
@@ -17189,7 +17196,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>445</v>
       </c>
@@ -17239,7 +17246,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>447</v>
       </c>
@@ -17289,7 +17296,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>449</v>
       </c>
@@ -17339,7 +17346,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>452</v>
       </c>
@@ -17389,7 +17396,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>454</v>
       </c>
@@ -17439,7 +17446,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>457</v>
       </c>
@@ -17489,7 +17496,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>461</v>
       </c>
@@ -17539,7 +17546,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>464</v>
       </c>
@@ -17589,7 +17596,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>466</v>
       </c>
@@ -17639,7 +17646,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>469</v>
       </c>
@@ -17689,7 +17696,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>471</v>
       </c>
@@ -17739,7 +17746,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>474</v>
       </c>
@@ -17789,7 +17796,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>477</v>
       </c>
@@ -17839,7 +17846,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>480</v>
       </c>
@@ -17889,7 +17896,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>483</v>
       </c>
@@ -17939,7 +17946,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>487</v>
       </c>
@@ -17989,7 +17996,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>490</v>
       </c>
@@ -18039,7 +18046,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>493</v>
       </c>
@@ -18089,7 +18096,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>496</v>
       </c>
@@ -18139,7 +18146,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>499</v>
       </c>
@@ -18189,7 +18196,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>502</v>
       </c>
@@ -18239,7 +18246,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>505</v>
       </c>
@@ -18289,7 +18296,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>508</v>
       </c>
@@ -18339,7 +18346,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>512</v>
       </c>
@@ -18389,7 +18396,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>515</v>
       </c>
@@ -18439,7 +18446,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>519</v>
       </c>
@@ -18489,7 +18496,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>522</v>
       </c>
@@ -18539,7 +18546,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>524</v>
       </c>
@@ -18589,7 +18596,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>527</v>
       </c>
@@ -18639,7 +18646,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>530</v>
       </c>
@@ -18689,7 +18696,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>533</v>
       </c>
@@ -18739,7 +18746,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>536</v>
       </c>
@@ -18789,7 +18796,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>538</v>
       </c>
@@ -18839,7 +18846,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>541</v>
       </c>
@@ -18889,7 +18896,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>544</v>
       </c>
@@ -18939,7 +18946,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>547</v>
       </c>
@@ -18989,7 +18996,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>551</v>
       </c>
@@ -19039,7 +19046,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>553</v>
       </c>
@@ -19089,7 +19096,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>557</v>
       </c>
@@ -19139,7 +19146,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>559</v>
       </c>
@@ -19189,7 +19196,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>562</v>
       </c>
@@ -19239,7 +19246,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>565</v>
       </c>
@@ -19289,7 +19296,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>568</v>
       </c>
@@ -19339,7 +19346,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>571</v>
       </c>
@@ -19386,7 +19393,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>574</v>
       </c>
@@ -19436,7 +19443,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>579</v>
       </c>
@@ -19486,7 +19493,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>583</v>
       </c>
@@ -19536,7 +19543,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>586</v>
       </c>
@@ -19586,7 +19593,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>588</v>
       </c>
@@ -19636,7 +19643,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>590</v>
       </c>
@@ -19686,7 +19693,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>592</v>
       </c>
@@ -19736,7 +19743,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>595</v>
       </c>
@@ -19786,7 +19793,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>597</v>
       </c>
@@ -19836,7 +19843,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>600</v>
       </c>
@@ -19886,7 +19893,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>602</v>
       </c>
@@ -19936,7 +19943,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>605</v>
       </c>
@@ -19986,7 +19993,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>607</v>
       </c>
@@ -20036,7 +20043,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>609</v>
       </c>
@@ -20086,7 +20093,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>612</v>
       </c>
@@ -20136,7 +20143,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>614</v>
       </c>
@@ -20186,7 +20193,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>617</v>
       </c>
@@ -20236,7 +20243,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>620</v>
       </c>
@@ -20286,7 +20293,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>623</v>
       </c>
@@ -20336,7 +20343,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>625</v>
       </c>
@@ -20386,7 +20393,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>627</v>
       </c>
@@ -20436,7 +20443,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>631</v>
       </c>
@@ -20486,7 +20493,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>634</v>
       </c>
@@ -20536,7 +20543,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>636</v>
       </c>
@@ -20586,7 +20593,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>639</v>
       </c>
@@ -20636,7 +20643,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>643</v>
       </c>
@@ -20686,7 +20693,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>646</v>
       </c>
@@ -20736,7 +20743,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>649</v>
       </c>
@@ -20786,7 +20793,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>653</v>
       </c>
@@ -20836,7 +20843,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>657</v>
       </c>
@@ -20886,7 +20893,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>660</v>
       </c>
@@ -20936,7 +20943,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>663</v>
       </c>
@@ -20986,7 +20993,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>666</v>
       </c>
@@ -21036,7 +21043,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>668</v>
       </c>
@@ -21086,7 +21093,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>671</v>
       </c>
@@ -21136,7 +21143,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>674</v>
       </c>
@@ -21186,7 +21193,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>677</v>
       </c>
@@ -21236,7 +21243,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>679</v>
       </c>
@@ -21286,7 +21293,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>683</v>
       </c>
@@ -21336,7 +21343,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>685</v>
       </c>
@@ -21386,7 +21393,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>688</v>
       </c>
@@ -21436,7 +21443,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>691</v>
       </c>
@@ -21486,7 +21493,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>693</v>
       </c>
@@ -21536,7 +21543,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>696</v>
       </c>
@@ -21586,7 +21593,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>699</v>
       </c>
@@ -21636,7 +21643,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>702</v>
       </c>
@@ -21686,7 +21693,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>704</v>
       </c>
@@ -21736,7 +21743,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>707</v>
       </c>
@@ -21786,7 +21793,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>712</v>
       </c>
@@ -21836,7 +21843,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>715</v>
       </c>
@@ -21886,7 +21893,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>718</v>
       </c>
@@ -21936,7 +21943,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>721</v>
       </c>
@@ -21986,7 +21993,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>724</v>
       </c>
@@ -22036,7 +22043,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>727</v>
       </c>
@@ -22086,7 +22093,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>732</v>
       </c>
@@ -22136,7 +22143,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>735</v>
       </c>
@@ -22186,7 +22193,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>738</v>
       </c>
@@ -22236,7 +22243,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>741</v>
       </c>
@@ -22283,7 +22290,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>742</v>
       </c>
@@ -22333,7 +22340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>749</v>
       </c>
@@ -22383,7 +22390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>753</v>
       </c>
@@ -22433,7 +22440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>757</v>
       </c>
@@ -22483,7 +22490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>759</v>
       </c>
@@ -22533,7 +22540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>763</v>
       </c>
@@ -22583,7 +22590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>765</v>
       </c>
@@ -22633,7 +22640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>767</v>
       </c>
@@ -22683,7 +22690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>769</v>
       </c>
@@ -22733,7 +22740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>771</v>
       </c>
@@ -22783,7 +22790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>773</v>
       </c>
@@ -22833,7 +22840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>776</v>
       </c>
@@ -22883,7 +22890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>780</v>
       </c>
@@ -22933,7 +22940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>784</v>
       </c>
@@ -22983,7 +22990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>787</v>
       </c>
@@ -23033,7 +23040,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>790</v>
       </c>
@@ -23083,7 +23090,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>793</v>
       </c>
@@ -23133,7 +23140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>796</v>
       </c>
@@ -23183,7 +23190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>798</v>
       </c>
@@ -23233,7 +23240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>801</v>
       </c>
@@ -23283,7 +23290,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>804</v>
       </c>
@@ -23333,7 +23340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>808</v>
       </c>
@@ -23383,7 +23390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>811</v>
       </c>
@@ -23433,7 +23440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>815</v>
       </c>
@@ -23483,7 +23490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>818</v>
       </c>
@@ -23533,7 +23540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>821</v>
       </c>
@@ -23583,7 +23590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>824</v>
       </c>
@@ -23633,7 +23640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>828</v>
       </c>
@@ -23683,7 +23690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>831</v>
       </c>
@@ -23733,7 +23740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>833</v>
       </c>
@@ -23783,7 +23790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>835</v>
       </c>
@@ -23833,7 +23840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>837</v>
       </c>
@@ -23883,7 +23890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>839</v>
       </c>
@@ -23933,7 +23940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>843</v>
       </c>
@@ -23983,7 +23990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>845</v>
       </c>
@@ -24033,7 +24040,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>849</v>
       </c>
@@ -24083,7 +24090,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>851</v>
       </c>
@@ -24133,7 +24140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>855</v>
       </c>
@@ -24183,7 +24190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>859</v>
       </c>
@@ -24233,7 +24240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>862</v>
       </c>
@@ -24283,7 +24290,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>864</v>
       </c>
@@ -24333,7 +24340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>867</v>
       </c>
@@ -24383,7 +24390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>869</v>
       </c>
@@ -24433,7 +24440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>873</v>
       </c>
@@ -24483,7 +24490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>876</v>
       </c>
@@ -24533,7 +24540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>879</v>
       </c>
@@ -24583,7 +24590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>882</v>
       </c>
@@ -24633,7 +24640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>886</v>
       </c>
@@ -24683,7 +24690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>889</v>
       </c>
@@ -24733,7 +24740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>893</v>
       </c>
@@ -24783,7 +24790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>896</v>
       </c>
@@ -24833,7 +24840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>898</v>
       </c>
@@ -24883,7 +24890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>900</v>
       </c>
@@ -24933,7 +24940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>902</v>
       </c>
@@ -24983,7 +24990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>904</v>
       </c>
@@ -25033,7 +25040,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>906</v>
       </c>
@@ -25083,7 +25090,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>910</v>
       </c>
@@ -25133,7 +25140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>912</v>
       </c>
@@ -25183,7 +25190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>915</v>
       </c>
@@ -25233,7 +25240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>918</v>
       </c>
@@ -25283,7 +25290,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>920</v>
       </c>
@@ -25333,7 +25340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>923</v>
       </c>
@@ -25383,7 +25390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>925</v>
       </c>
@@ -25433,7 +25440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>927</v>
       </c>
@@ -25483,7 +25490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>930</v>
       </c>
@@ -25533,7 +25540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>934</v>
       </c>
@@ -25583,7 +25590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>938</v>
       </c>
@@ -25633,7 +25640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>941</v>
       </c>
@@ -25683,7 +25690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>944</v>
       </c>
@@ -25733,7 +25740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>948</v>
       </c>
@@ -25783,7 +25790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>951</v>
       </c>
@@ -25833,7 +25840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>955</v>
       </c>
@@ -25880,7 +25887,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>956</v>
       </c>
@@ -25927,7 +25934,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>958</v>
       </c>
@@ -25974,7 +25981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>959</v>
       </c>
@@ -26021,7 +26028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>960</v>
       </c>
@@ -26068,7 +26075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>961</v>
       </c>
@@ -26118,7 +26125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>966</v>
       </c>
@@ -26168,7 +26175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>970</v>
       </c>
@@ -26218,7 +26225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>974</v>
       </c>
@@ -26268,7 +26275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>976</v>
       </c>
@@ -26318,7 +26325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>980</v>
       </c>
@@ -26368,7 +26375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>983</v>
       </c>
@@ -26418,7 +26425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>987</v>
       </c>
@@ -26468,7 +26475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>991</v>
       </c>
@@ -26518,7 +26525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>994</v>
       </c>
@@ -26568,7 +26575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>998</v>
       </c>
@@ -26618,7 +26625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1001</v>
       </c>
@@ -26668,7 +26675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1004</v>
       </c>
@@ -26718,7 +26725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1006</v>
       </c>
@@ -26768,7 +26775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1009</v>
       </c>
@@ -26818,7 +26825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1012</v>
       </c>
@@ -26868,7 +26875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1014</v>
       </c>
@@ -26918,7 +26925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1018</v>
       </c>
@@ -26968,7 +26975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1021</v>
       </c>
@@ -27018,7 +27025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1024</v>
       </c>
@@ -27068,7 +27075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1028</v>
       </c>
@@ -27118,7 +27125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1031</v>
       </c>
@@ -27168,7 +27175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1033</v>
       </c>
@@ -27218,7 +27225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="351" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1036</v>
       </c>
@@ -27268,7 +27275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1038</v>
       </c>
@@ -27318,7 +27325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="353" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1041</v>
       </c>
@@ -27368,7 +27375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="354" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1044</v>
       </c>
@@ -27418,7 +27425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="355" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1046</v>
       </c>
@@ -27468,7 +27475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1049</v>
       </c>
@@ -27518,7 +27525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="357" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1051</v>
       </c>
@@ -27568,7 +27575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="358" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1054</v>
       </c>
@@ -27618,7 +27625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="359" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1057</v>
       </c>
@@ -27668,7 +27675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="360" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1061</v>
       </c>
@@ -27718,7 +27725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="361" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1064</v>
       </c>
@@ -27768,7 +27775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="362" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1066</v>
       </c>
@@ -27818,7 +27825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="363" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1070</v>
       </c>
@@ -27868,7 +27875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="364" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1074</v>
       </c>
@@ -27918,7 +27925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="365" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1078</v>
       </c>
@@ -27968,7 +27975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="366" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1081</v>
       </c>
@@ -28018,7 +28025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="367" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1083</v>
       </c>
@@ -28068,7 +28075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="368" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1086</v>
       </c>
@@ -28118,7 +28125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="369" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1088</v>
       </c>
@@ -28168,7 +28175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="370" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1091</v>
       </c>
@@ -28218,7 +28225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="371" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1094</v>
       </c>
@@ -28268,7 +28275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="372" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1096</v>
       </c>
@@ -28318,7 +28325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="373" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1099</v>
       </c>
@@ -28368,7 +28375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1101</v>
       </c>
@@ -28418,7 +28425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1104</v>
       </c>
@@ -28468,7 +28475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="376" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1107</v>
       </c>
@@ -28518,7 +28525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="377" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>1109</v>
       </c>
@@ -28568,7 +28575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="378" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>1113</v>
       </c>
@@ -28618,7 +28625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="379" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>1116</v>
       </c>
@@ -28668,7 +28675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="380" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>1119</v>
       </c>
@@ -28718,7 +28725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="381" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>1123</v>
       </c>
@@ -28768,7 +28775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="382" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>1126</v>
       </c>
@@ -28818,7 +28825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="383" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1130</v>
       </c>
@@ -28868,7 +28875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="384" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>1133</v>
       </c>
@@ -28918,7 +28925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="385" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1135</v>
       </c>
@@ -28968,7 +28975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="386" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1138</v>
       </c>
@@ -29018,7 +29025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1140</v>
       </c>
@@ -29068,7 +29075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="388" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1143</v>
       </c>
@@ -29118,7 +29125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="389" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1145</v>
       </c>
@@ -29168,7 +29175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="390" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1148</v>
       </c>
@@ -29218,7 +29225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="391" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1151</v>
       </c>
@@ -29268,7 +29275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="392" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1153</v>
       </c>
@@ -29318,7 +29325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="393" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1156</v>
       </c>
@@ -29368,7 +29375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="394" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1158</v>
       </c>
@@ -29418,7 +29425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="395" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1161</v>
       </c>
@@ -29468,7 +29475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="396" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1164</v>
       </c>
@@ -29518,7 +29525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="397" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1168</v>
       </c>
@@ -29568,7 +29575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="398" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1173</v>
       </c>
@@ -29618,7 +29625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="399" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1176</v>
       </c>
@@ -29668,7 +29675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="400" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1179</v>
       </c>
@@ -29718,7 +29725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="401" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1181</v>
       </c>
@@ -29768,7 +29775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="402" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1183</v>
       </c>
@@ -29818,7 +29825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1186</v>
       </c>
@@ -29868,7 +29875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1190</v>
       </c>
@@ -29918,7 +29925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1194</v>
       </c>
@@ -29968,7 +29975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1198</v>
       </c>
@@ -30018,7 +30025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="407" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1200</v>
       </c>
@@ -30068,7 +30075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1202</v>
       </c>
@@ -30118,7 +30125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1205</v>
       </c>
@@ -30168,7 +30175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="410" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1207</v>
       </c>
@@ -30218,7 +30225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>1209</v>
       </c>
@@ -30268,7 +30275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1212</v>
       </c>
@@ -30318,7 +30325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="413" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1214</v>
       </c>
@@ -30368,7 +30375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="414" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1218</v>
       </c>
@@ -30418,7 +30425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1221</v>
       </c>
@@ -30468,7 +30475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="416" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1224</v>
       </c>
@@ -30518,7 +30525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="417" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1227</v>
       </c>
@@ -30568,7 +30575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="418" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1229</v>
       </c>
@@ -30618,7 +30625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="419" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1231</v>
       </c>
@@ -30668,7 +30675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="420" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1235</v>
       </c>
@@ -30718,7 +30725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="421" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1237</v>
       </c>
@@ -30768,7 +30775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="422" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1240</v>
       </c>
@@ -30818,7 +30825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="423" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1243</v>
       </c>
@@ -30868,7 +30875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="424" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1247</v>
       </c>
@@ -30918,7 +30925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="425" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1249</v>
       </c>
@@ -30968,7 +30975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="426" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1251</v>
       </c>
@@ -31018,7 +31025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="427" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1254</v>
       </c>
@@ -31068,7 +31075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="428" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1257</v>
       </c>
@@ -31118,7 +31125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="429" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1261</v>
       </c>
@@ -31168,7 +31175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="430" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1263</v>
       </c>
@@ -31218,7 +31225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="431" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1266</v>
       </c>
@@ -31268,7 +31275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="432" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1268</v>
       </c>
@@ -31318,7 +31325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="433" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1271</v>
       </c>
@@ -31368,7 +31375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="434" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1274</v>
       </c>
@@ -31418,7 +31425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="435" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1278</v>
       </c>
@@ -31468,7 +31475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="436" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1281</v>
       </c>
@@ -31518,7 +31525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="437" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1285</v>
       </c>
@@ -31568,7 +31575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="438" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1287</v>
       </c>
@@ -31618,7 +31625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="439" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1289</v>
       </c>
@@ -31668,7 +31675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="440" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1292</v>
       </c>
@@ -31718,7 +31725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="441" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1294</v>
       </c>
@@ -31768,7 +31775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="442" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1296</v>
       </c>
@@ -31818,7 +31825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="443" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1299</v>
       </c>
@@ -31868,7 +31875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="444" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1301</v>
       </c>
@@ -31918,7 +31925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="445" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1304</v>
       </c>
@@ -31968,7 +31975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="446" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1306</v>
       </c>
@@ -32018,7 +32025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="447" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1309</v>
       </c>
@@ -32068,7 +32075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="448" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1311</v>
       </c>
@@ -32118,7 +32125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="449" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1314</v>
       </c>
@@ -32168,7 +32175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="450" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1316</v>
       </c>
@@ -32218,7 +32225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="451" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1319</v>
       </c>
@@ -32268,7 +32275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="452" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1322</v>
       </c>
@@ -32318,7 +32325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="453" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1326</v>
       </c>
@@ -32368,7 +32375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="454" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1329</v>
       </c>
@@ -32418,7 +32425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="455" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1333</v>
       </c>
@@ -32468,7 +32475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="456" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1335</v>
       </c>
@@ -32518,7 +32525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="457" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1338</v>
       </c>
@@ -32568,7 +32575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="458" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1340</v>
       </c>
@@ -32618,7 +32625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="459" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1343</v>
       </c>
@@ -32668,7 +32675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="460" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1345</v>
       </c>
@@ -32718,7 +32725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="461" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1348</v>
       </c>
@@ -32768,7 +32775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="462" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1350</v>
       </c>
@@ -32818,7 +32825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="463" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1353</v>
       </c>
@@ -32868,7 +32875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="464" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1355</v>
       </c>
@@ -32918,7 +32925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="465" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1357</v>
       </c>
@@ -32968,7 +32975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="466" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1361</v>
       </c>
@@ -33018,7 +33025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="467" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1363</v>
       </c>
@@ -33068,7 +33075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="468" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1366</v>
       </c>
@@ -33118,7 +33125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="469" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1368</v>
       </c>
@@ -33168,7 +33175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="470" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1371</v>
       </c>
@@ -33218,7 +33225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="471" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1373</v>
       </c>
@@ -33268,7 +33275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="472" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1376</v>
       </c>
@@ -33318,7 +33325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="473" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1378</v>
       </c>
@@ -33368,7 +33375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="474" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1381</v>
       </c>
@@ -33418,7 +33425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="475" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1385</v>
       </c>
@@ -33468,7 +33475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="476" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1389</v>
       </c>
@@ -33518,7 +33525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="477" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1392</v>
       </c>
@@ -33568,7 +33575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="478" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1396</v>
       </c>
@@ -33618,7 +33625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="479" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1398</v>
       </c>
@@ -33668,7 +33675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="480" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1400</v>
       </c>
@@ -33718,7 +33725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="481" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1404</v>
       </c>
@@ -33768,7 +33775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="482" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1407</v>
       </c>
@@ -33818,7 +33825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="483" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1411</v>
       </c>
@@ -33868,7 +33875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="484" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1413</v>
       </c>
@@ -33918,7 +33925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="485" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1415</v>
       </c>
@@ -33968,7 +33975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="486" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1418</v>
       </c>
@@ -34018,7 +34025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="487" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1421</v>
       </c>
@@ -34068,7 +34075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="488" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1425</v>
       </c>
@@ -34118,7 +34125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="489" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1427</v>
       </c>
@@ -34168,7 +34175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="490" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1429</v>
       </c>
@@ -34218,7 +34225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="491" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1433</v>
       </c>
@@ -34268,7 +34275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="492" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1435</v>
       </c>
@@ -34318,7 +34325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="493" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1438</v>
       </c>
@@ -34368,7 +34375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="494" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>1440</v>
       </c>
@@ -34418,7 +34425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="495" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>1444</v>
       </c>
@@ -34468,7 +34475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="496" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>1447</v>
       </c>
@@ -34518,7 +34525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="497" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>1451</v>
       </c>
@@ -34568,7 +34575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="498" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>1454</v>
       </c>
@@ -34618,7 +34625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="499" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>1456</v>
       </c>
@@ -34668,7 +34675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="500" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>1459</v>
       </c>
@@ -34718,7 +34725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="501" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>1461</v>
       </c>
@@ -34768,7 +34775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="502" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>1463</v>
       </c>
@@ -34818,7 +34825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="503" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>1465</v>
       </c>
@@ -34868,7 +34875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="504" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>1468</v>
       </c>
@@ -34918,7 +34925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="505" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>1472</v>
       </c>
@@ -34968,7 +34975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="506" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>1476</v>
       </c>
@@ -35018,7 +35025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="507" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>1478</v>
       </c>
@@ -35068,7 +35075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="508" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>1482</v>
       </c>
@@ -35118,7 +35125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="509" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>1485</v>
       </c>
@@ -35168,7 +35175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="510" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>1488</v>
       </c>
@@ -35218,7 +35225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="511" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1490</v>
       </c>
@@ -35268,7 +35275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="512" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>1493</v>
       </c>
@@ -35318,7 +35325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="513" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>1496</v>
       </c>
@@ -35368,7 +35375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="514" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>1500</v>
       </c>
@@ -35418,7 +35425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="515" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1502</v>
       </c>
@@ -35468,7 +35475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="516" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1506</v>
       </c>
@@ -35518,7 +35525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="517" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>1508</v>
       </c>
@@ -35568,7 +35575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="518" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1512</v>
       </c>
@@ -35618,7 +35625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="519" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1515</v>
       </c>
@@ -35668,7 +35675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="520" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1519</v>
       </c>
@@ -35718,7 +35725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="521" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1522</v>
       </c>
@@ -35768,7 +35775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="522" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1525</v>
       </c>
@@ -35818,7 +35825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="523" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1527</v>
       </c>
@@ -35868,7 +35875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="524" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1529</v>
       </c>
@@ -35918,7 +35925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="525" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1531</v>
       </c>
@@ -35968,7 +35975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="526" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1534</v>
       </c>
@@ -36018,7 +36025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="527" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1536</v>
       </c>
@@ -36068,7 +36075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="528" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>1539</v>
       </c>
@@ -36118,7 +36125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="529" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1542</v>
       </c>
@@ -36168,7 +36175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="530" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1544</v>
       </c>
@@ -36218,7 +36225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="531" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>1546</v>
       </c>
@@ -36268,7 +36275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="532" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>1551</v>
       </c>
@@ -36318,7 +36325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="533" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>1554</v>
       </c>
@@ -36368,7 +36375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="534" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>1557</v>
       </c>
@@ -36418,7 +36425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="535" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>1561</v>
       </c>
@@ -36468,7 +36475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="536" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>1563</v>
       </c>
@@ -36518,7 +36525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="537" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>1566</v>
       </c>
@@ -36568,7 +36575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="538" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>1569</v>
       </c>
@@ -36618,7 +36625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="539" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1571</v>
       </c>
@@ -36668,7 +36675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="540" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>1573</v>
       </c>
@@ -36718,7 +36725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="541" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>1575</v>
       </c>
@@ -36771,7 +36778,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="542" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1581</v>
       </c>
@@ -36824,7 +36831,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="543" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1584</v>
       </c>
@@ -36877,7 +36884,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="544" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1587</v>
       </c>
@@ -36930,7 +36937,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="545" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>1590</v>
       </c>
@@ -36983,7 +36990,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="546" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>1593</v>
       </c>
@@ -37036,7 +37043,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="547" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>1596</v>
       </c>
@@ -37089,7 +37096,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="548" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>1599</v>
       </c>
@@ -37139,7 +37146,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="549" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>1601</v>
       </c>
@@ -37189,7 +37196,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="550" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1603</v>
       </c>
@@ -37242,7 +37249,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="551" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>1607</v>
       </c>
@@ -37295,7 +37302,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="552" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>1610</v>
       </c>
@@ -37348,7 +37355,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="553" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>1613</v>
       </c>
@@ -37401,7 +37408,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="554" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>1616</v>
       </c>
@@ -39587,7 +39594,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="600" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>1723</v>
       </c>
@@ -39637,7 +39644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="601" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>1730</v>
       </c>
@@ -39687,7 +39694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="602" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>1732</v>
       </c>
@@ -39737,7 +39744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="603" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>1734</v>
       </c>
@@ -39787,7 +39794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="604" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>1736</v>
       </c>
@@ -39837,7 +39844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="605" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>1738</v>
       </c>
@@ -39887,7 +39894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="606" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>1741</v>
       </c>
@@ -39937,7 +39944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="607" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>1743</v>
       </c>
@@ -39987,7 +39994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="608" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>1746</v>
       </c>
@@ -40037,7 +40044,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="609" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>1748</v>
       </c>
@@ -40087,7 +40094,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="610" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>1750</v>
       </c>
@@ -40137,7 +40144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>1752</v>
       </c>
@@ -40187,7 +40194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="612" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>1755</v>
       </c>
@@ -40237,7 +40244,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="613" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>1757</v>
       </c>
@@ -40287,7 +40294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="614" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>1760</v>
       </c>
@@ -40337,7 +40344,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="615" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>1762</v>
       </c>
@@ -40387,7 +40394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>1764</v>
       </c>
@@ -40437,7 +40444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>1767</v>
       </c>
@@ -40487,7 +40494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="618" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>1769</v>
       </c>
@@ -40537,7 +40544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="619" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>1771</v>
       </c>
@@ -40587,7 +40594,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>1776</v>
       </c>
@@ -40637,7 +40644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>1778</v>
       </c>
@@ -40687,7 +40694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="622" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>1781</v>
       </c>
@@ -40737,7 +40744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>1785</v>
       </c>
@@ -40787,7 +40794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>1788</v>
       </c>
@@ -40837,7 +40844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="625" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>1791</v>
       </c>
@@ -40887,7 +40894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="626" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>1793</v>
       </c>
@@ -40937,7 +40944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="627" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>1796</v>
       </c>
@@ -40987,7 +40994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="628" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>1799</v>
       </c>
@@ -41037,7 +41044,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="629" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>1806</v>
       </c>
@@ -41087,7 +41094,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="630" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>1809</v>
       </c>
@@ -41137,7 +41144,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="631" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>1812</v>
       </c>
@@ -41187,7 +41194,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="632" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>1814</v>
       </c>
@@ -41237,7 +41244,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="633" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>1817</v>
       </c>
@@ -41287,7 +41294,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="634" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>1820</v>
       </c>
@@ -41337,7 +41344,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="635" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>1823</v>
       </c>
@@ -41387,7 +41394,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="636" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>1826</v>
       </c>
@@ -41437,7 +41444,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="637" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>1828</v>
       </c>
@@ -41487,7 +41494,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="638" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>1831</v>
       </c>
@@ -41537,7 +41544,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="639" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>1834</v>
       </c>
@@ -41587,7 +41594,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="640" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>1839</v>
       </c>
@@ -41637,7 +41644,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="641" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>1842</v>
       </c>
@@ -41687,7 +41694,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="642" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>1845</v>
       </c>
@@ -41737,7 +41744,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="643" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>1848</v>
       </c>
@@ -41787,7 +41794,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="644" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>1853</v>
       </c>
@@ -41837,7 +41844,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="645" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>1856</v>
       </c>
@@ -41887,7 +41894,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="646" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>1859</v>
       </c>
@@ -41937,7 +41944,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="647" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>1862</v>
       </c>
@@ -41987,7 +41994,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="648" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>1866</v>
       </c>
@@ -42037,7 +42044,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="649" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>1869</v>
       </c>
@@ -42087,7 +42094,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="650" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>1872</v>
       </c>
@@ -42137,7 +42144,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="651" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>1877</v>
       </c>
@@ -42187,7 +42194,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="652" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>1880</v>
       </c>
@@ -42237,7 +42244,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="653" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>1884</v>
       </c>
@@ -42287,7 +42294,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="654" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>1888</v>
       </c>
@@ -42337,7 +42344,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="655" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>1890</v>
       </c>
@@ -42387,7 +42394,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="656" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>1892</v>
       </c>
@@ -42437,7 +42444,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="657" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>1895</v>
       </c>
@@ -42487,7 +42494,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="658" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>1898</v>
       </c>
@@ -42537,7 +42544,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="659" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>1900</v>
       </c>
@@ -42587,7 +42594,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="660" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>1902</v>
       </c>
@@ -42637,7 +42644,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="661" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>1905</v>
       </c>
@@ -42687,7 +42694,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="662" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>1908</v>
       </c>
@@ -42737,7 +42744,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="663" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>1911</v>
       </c>
@@ -42787,7 +42794,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="664" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>1914</v>
       </c>
@@ -42837,7 +42844,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="665" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>1917</v>
       </c>
@@ -42887,7 +42894,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="666" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>1919</v>
       </c>
@@ -42937,7 +42944,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="667" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>1921</v>
       </c>
@@ -42987,7 +42994,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="668" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>1924</v>
       </c>
@@ -43037,7 +43044,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="669" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>1927</v>
       </c>
@@ -43087,7 +43094,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="670" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>1929</v>
       </c>
@@ -43137,7 +43144,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="671" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>1932</v>
       </c>
@@ -43187,7 +43194,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="672" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>1935</v>
       </c>
@@ -43237,7 +43244,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="673" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>1938</v>
       </c>
@@ -43287,7 +43294,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="674" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>1941</v>
       </c>
@@ -43337,7 +43344,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="675" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>1944</v>
       </c>
@@ -43387,7 +43394,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="676" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>1946</v>
       </c>
@@ -43437,7 +43444,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="677" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>1949</v>
       </c>
@@ -43487,7 +43494,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="678" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>1952</v>
       </c>
@@ -43537,7 +43544,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="679" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>1954</v>
       </c>
@@ -43587,7 +43594,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="680" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>1956</v>
       </c>
@@ -43637,7 +43644,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="681" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>1959</v>
       </c>
@@ -43687,7 +43694,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="682" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>1962</v>
       </c>
@@ -43737,7 +43744,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="683" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>1965</v>
       </c>
@@ -43787,7 +43794,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="684" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>1968</v>
       </c>
@@ -43837,7 +43844,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="685" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>1970</v>
       </c>
@@ -43887,7 +43894,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="686" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>1973</v>
       </c>
@@ -43937,7 +43944,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="687" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>1977</v>
       </c>
@@ -43987,7 +43994,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="688" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>1982</v>
       </c>
@@ -44037,7 +44044,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="689" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>1985</v>
       </c>
@@ -44087,7 +44094,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="690" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>1988</v>
       </c>
@@ -44137,7 +44144,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="691" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>1991</v>
       </c>
@@ -44187,7 +44194,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="692" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>1994</v>
       </c>
@@ -44234,7 +44241,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="693" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>1997</v>
       </c>
@@ -44284,7 +44291,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="694" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>2002</v>
       </c>
@@ -44334,7 +44341,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="695" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>2006</v>
       </c>
@@ -44384,7 +44391,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="696" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>2009</v>
       </c>
@@ -44434,7 +44441,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="697" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>2012</v>
       </c>
@@ -44484,7 +44491,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="698" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>2016</v>
       </c>
@@ -44534,7 +44541,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="699" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>2021</v>
       </c>
@@ -44584,7 +44591,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="700" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>2024</v>
       </c>
@@ -44637,7 +44644,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="701" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>2030</v>
       </c>
@@ -44687,7 +44694,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="702" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>2033</v>
       </c>
@@ -44737,7 +44744,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="703" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>2036</v>
       </c>
@@ -44787,7 +44794,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="704" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>2039</v>
       </c>
@@ -44837,7 +44844,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="705" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>2041</v>
       </c>
@@ -44890,7 +44897,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="706" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>2044</v>
       </c>
@@ -44943,7 +44950,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="707" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>2047</v>
       </c>
@@ -44996,7 +45003,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="708" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>2051</v>
       </c>
@@ -45046,7 +45053,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="709" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>2054</v>
       </c>
@@ -45096,7 +45103,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="710" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>2057</v>
       </c>
@@ -45146,7 +45153,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="711" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>2060</v>
       </c>
@@ -45199,7 +45206,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="712" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>2063</v>
       </c>
@@ -45252,7 +45259,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="713" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>2066</v>
       </c>
@@ -45305,7 +45312,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="714" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>2069</v>
       </c>
@@ -45358,7 +45365,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="715" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>2073</v>
       </c>
@@ -45408,7 +45415,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="716" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>2076</v>
       </c>
@@ -45461,7 +45468,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="717" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>2079</v>
       </c>
@@ -45514,7 +45521,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="718" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>2081</v>
       </c>
@@ -45567,7 +45574,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="719" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>2084</v>
       </c>
@@ -45620,7 +45627,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="720" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>2087</v>
       </c>
@@ -45673,7 +45680,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="721" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>2090</v>
       </c>
@@ -45726,7 +45733,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="722" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>2092</v>
       </c>
@@ -45776,7 +45783,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="723" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>2095</v>
       </c>
@@ -45823,7 +45830,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="724" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>2100</v>
       </c>
@@ -45870,7 +45877,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="725" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>2103</v>
       </c>
@@ -45917,7 +45924,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="726" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>2105</v>
       </c>
@@ -45964,7 +45971,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="727" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>2107</v>
       </c>
@@ -46011,7 +46018,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="728" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>2109</v>
       </c>
@@ -46058,7 +46065,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="729" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>2111</v>
       </c>
@@ -46105,7 +46112,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="730" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>2113</v>
       </c>
@@ -46152,7 +46159,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="731" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>2115</v>
       </c>
@@ -46199,7 +46206,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="732" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>2117</v>
       </c>
@@ -46246,7 +46253,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="733" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>2119</v>
       </c>
@@ -46293,7 +46300,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="734" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>2121</v>
       </c>
@@ -46343,7 +46350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="735" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>2129</v>
       </c>
@@ -46393,7 +46400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="736" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>2132</v>
       </c>
@@ -46443,7 +46450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="737" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>2136</v>
       </c>
@@ -46493,7 +46500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="738" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>2139</v>
       </c>
@@ -46543,7 +46550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="739" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>2143</v>
       </c>
@@ -46593,7 +46600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="740" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>2146</v>
       </c>
@@ -46643,7 +46650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="741" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>2150</v>
       </c>
@@ -46693,7 +46700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="742" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>2155</v>
       </c>
@@ -46743,7 +46750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="743" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>2159</v>
       </c>
@@ -46793,7 +46800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="744" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>2161</v>
       </c>
@@ -46843,7 +46850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="745" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>2164</v>
       </c>
@@ -46893,7 +46900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="746" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>2167</v>
       </c>
@@ -46943,7 +46950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="747" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>2171</v>
       </c>
@@ -46993,7 +47000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="748" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>2173</v>
       </c>
@@ -47043,7 +47050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="749" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>2176</v>
       </c>
@@ -47093,7 +47100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="750" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>2180</v>
       </c>
@@ -47143,7 +47150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="751" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>2182</v>
       </c>
@@ -47193,7 +47200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="752" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>2185</v>
       </c>
@@ -47243,7 +47250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="753" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>2188</v>
       </c>
@@ -47293,7 +47300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="754" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>2192</v>
       </c>
@@ -47343,7 +47350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="755" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>2194</v>
       </c>
@@ -47393,7 +47400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="756" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>2197</v>
       </c>
@@ -47443,7 +47450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="757" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>2201</v>
       </c>
@@ -47493,7 +47500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="758" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>2203</v>
       </c>
@@ -47543,7 +47550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="759" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>2206</v>
       </c>
@@ -47593,7 +47600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="760" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>2209</v>
       </c>
@@ -47643,7 +47650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="761" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>2213</v>
       </c>
@@ -47693,7 +47700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="762" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>2215</v>
       </c>
@@ -47743,7 +47750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="763" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>2217</v>
       </c>
@@ -47793,7 +47800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="764" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>2220</v>
       </c>
@@ -47843,7 +47850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="765" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>2222</v>
       </c>
@@ -47893,7 +47900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="766" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>2224</v>
       </c>
@@ -47943,7 +47950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="767" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>2228</v>
       </c>
@@ -47993,7 +48000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="768" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>2231</v>
       </c>
@@ -48043,7 +48050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="769" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>2235</v>
       </c>
@@ -48093,7 +48100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="770" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>2237</v>
       </c>
@@ -48143,7 +48150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="771" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>2240</v>
       </c>
@@ -48193,7 +48200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="772" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>2242</v>
       </c>
@@ -48243,7 +48250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="773" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>2245</v>
       </c>
@@ -48293,7 +48300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="774" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>2249</v>
       </c>
@@ -48343,7 +48350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="775" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>2253</v>
       </c>
@@ -48393,7 +48400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="776" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>2256</v>
       </c>
@@ -48443,7 +48450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="777" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>2260</v>
       </c>
@@ -48493,7 +48500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="778" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>2262</v>
       </c>
@@ -48543,7 +48550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="779" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>2265</v>
       </c>
@@ -48593,7 +48600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="780" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>2267</v>
       </c>
@@ -48643,7 +48650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="781" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>2270</v>
       </c>
@@ -48693,7 +48700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="782" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>2274</v>
       </c>
@@ -48743,7 +48750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="783" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>2278</v>
       </c>
@@ -48793,7 +48800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="784" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>2281</v>
       </c>
@@ -48843,7 +48850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="785" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>2285</v>
       </c>
@@ -48893,7 +48900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="786" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>2287</v>
       </c>
@@ -48943,7 +48950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="787" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>2291</v>
       </c>
@@ -48993,7 +49000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="788" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>2295</v>
       </c>
@@ -49043,7 +49050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="789" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>2300</v>
       </c>
@@ -49093,7 +49100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="790" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>2305</v>
       </c>
@@ -49143,7 +49150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="791" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>2308</v>
       </c>
@@ -49193,7 +49200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="792" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>2311</v>
       </c>
@@ -49243,7 +49250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="793" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>2313</v>
       </c>
@@ -49293,7 +49300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="794" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>2316</v>
       </c>
@@ -49343,7 +49350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="795" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>2318</v>
       </c>
@@ -49393,7 +49400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="796" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>2321</v>
       </c>
@@ -49443,7 +49450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="797" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>2325</v>
       </c>
@@ -49493,7 +49500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="798" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>2329</v>
       </c>
@@ -49543,7 +49550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="799" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>2332</v>
       </c>
@@ -49593,7 +49600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="800" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>2336</v>
       </c>
@@ -49643,7 +49650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="801" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>2339</v>
       </c>
@@ -49693,7 +49700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="802" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>2342</v>
       </c>
@@ -49743,7 +49750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="803" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>2346</v>
       </c>
@@ -49793,7 +49800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="804" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>2349</v>
       </c>
@@ -49843,7 +49850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="805" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>2352</v>
       </c>
@@ -49893,7 +49900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="806" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>2355</v>
       </c>
@@ -49943,7 +49950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="807" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>2359</v>
       </c>
@@ -49993,7 +50000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="808" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>2361</v>
       </c>
@@ -50043,7 +50050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="809" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>2365</v>
       </c>
@@ -50093,7 +50100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="810" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>2367</v>
       </c>
@@ -50143,7 +50150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="811" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>2370</v>
       </c>
@@ -50193,7 +50200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="812" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>2373</v>
       </c>
@@ -50243,7 +50250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="813" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>2377</v>
       </c>
@@ -50293,7 +50300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="814" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>2380</v>
       </c>
@@ -50343,7 +50350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="815" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>2383</v>
       </c>
@@ -50393,7 +50400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="816" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>2386</v>
       </c>
@@ -50443,7 +50450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="817" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>2390</v>
       </c>
@@ -50493,7 +50500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="818" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>2392</v>
       </c>
@@ -50543,7 +50550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="819" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>2395</v>
       </c>
@@ -50593,7 +50600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="820" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>2397</v>
       </c>
@@ -50643,7 +50650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="821" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>2401</v>
       </c>
@@ -50693,7 +50700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="822" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>2404</v>
       </c>
@@ -50743,7 +50750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="823" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>2407</v>
       </c>
@@ -50793,7 +50800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="824" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>2411</v>
       </c>
@@ -50843,7 +50850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="825" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>2414</v>
       </c>
@@ -50893,7 +50900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="826" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>2417</v>
       </c>
@@ -50943,7 +50950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="827" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>2420</v>
       </c>
@@ -50990,7 +50997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="828" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>2424</v>
       </c>
@@ -51043,7 +51050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="829" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>2430</v>
       </c>
@@ -51096,7 +51103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="830" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>2435</v>
       </c>
@@ -51149,7 +51156,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="831" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>2438</v>
       </c>
@@ -51202,7 +51209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="832" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>2441</v>
       </c>
@@ -51255,7 +51262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="833" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>2445</v>
       </c>
@@ -51308,7 +51315,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="834" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>2448</v>
       </c>
@@ -51361,7 +51368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="835" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>2451</v>
       </c>
@@ -51414,7 +51421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="836" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>2454</v>
       </c>
@@ -51467,7 +51474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="837" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>2458</v>
       </c>
@@ -51520,7 +51527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="838" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>2462</v>
       </c>
@@ -51573,7 +51580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="839" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>2466</v>
       </c>
@@ -51626,7 +51633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="840" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>2469</v>
       </c>
@@ -51679,7 +51686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="841" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>2472</v>
       </c>
@@ -51732,7 +51739,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="842" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>2475</v>
       </c>
@@ -51785,7 +51792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="843" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>2478</v>
       </c>
@@ -51838,7 +51845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="844" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>2482</v>
       </c>
@@ -51891,7 +51898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="845" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>2485</v>
       </c>
@@ -51944,7 +51951,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="846" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>2488</v>
       </c>
@@ -51997,7 +52004,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="847" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>2491</v>
       </c>
@@ -52050,7 +52057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="848" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>2494</v>
       </c>
@@ -52103,7 +52110,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="849" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>2497</v>
       </c>
@@ -52156,7 +52163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="850" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>2500</v>
       </c>
@@ -52209,7 +52216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="851" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>2503</v>
       </c>
@@ -52262,7 +52269,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="852" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>2508</v>
       </c>
@@ -52315,7 +52322,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="853" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>2511</v>
       </c>
@@ -52368,7 +52375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="854" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>2514</v>
       </c>
@@ -52421,7 +52428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="855" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>2517</v>
       </c>
@@ -52474,7 +52481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="856" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>2520</v>
       </c>
@@ -52527,7 +52534,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="857" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>2524</v>
       </c>
@@ -52580,7 +52587,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="858" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>2527</v>
       </c>
@@ -52633,7 +52640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="859" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>2530</v>
       </c>
@@ -52683,7 +52690,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="860" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>2533</v>
       </c>
@@ -52733,7 +52740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="861" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>2538</v>
       </c>
@@ -52783,7 +52790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="862" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>2540</v>
       </c>
@@ -52833,7 +52840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="863" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>2542</v>
       </c>
@@ -52883,7 +52890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="864" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>2544</v>
       </c>
@@ -52933,7 +52940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="865" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>2546</v>
       </c>
@@ -52983,7 +52990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="866" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>2548</v>
       </c>
@@ -53033,7 +53040,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="867" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>2554</v>
       </c>
@@ -53083,7 +53090,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="868" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>2559</v>
       </c>
@@ -53144,7 +53151,7 @@
         <v>2564</v>
       </c>
       <c r="D869" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E869" t="s">
         <v>100</v>
@@ -53194,7 +53201,7 @@
         <v>2570</v>
       </c>
       <c r="D870" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E870" t="s">
         <v>100</v>
@@ -53244,7 +53251,7 @@
         <v>2573</v>
       </c>
       <c r="D871" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E871" t="s">
         <v>100</v>
@@ -53294,7 +53301,7 @@
         <v>2576</v>
       </c>
       <c r="D872" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E872" t="s">
         <v>100</v>
@@ -53344,7 +53351,7 @@
         <v>2579</v>
       </c>
       <c r="D873" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E873" t="s">
         <v>100</v>
@@ -53394,7 +53401,7 @@
         <v>2582</v>
       </c>
       <c r="D874" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E874" t="s">
         <v>100</v>
@@ -53444,7 +53451,7 @@
         <v>2586</v>
       </c>
       <c r="D875" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E875" t="s">
         <v>100</v>
@@ -53494,7 +53501,7 @@
         <v>2588</v>
       </c>
       <c r="D876" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E876" t="s">
         <v>100</v>
@@ -53544,7 +53551,7 @@
         <v>2591</v>
       </c>
       <c r="D877" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E877" t="s">
         <v>100</v>
@@ -53594,7 +53601,7 @@
         <v>2594</v>
       </c>
       <c r="D878" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E878" t="s">
         <v>100</v>
@@ -53644,7 +53651,7 @@
         <v>2597</v>
       </c>
       <c r="D879" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E879" t="s">
         <v>100</v>
@@ -53694,7 +53701,7 @@
         <v>2601</v>
       </c>
       <c r="D880" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E880" t="s">
         <v>100</v>
@@ -53744,7 +53751,7 @@
         <v>2601</v>
       </c>
       <c r="D881" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E881" t="s">
         <v>100</v>
@@ -53794,7 +53801,7 @@
         <v>2605</v>
       </c>
       <c r="D882" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E882" t="s">
         <v>100</v>
@@ -53844,7 +53851,7 @@
         <v>2608</v>
       </c>
       <c r="D883" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E883" t="s">
         <v>100</v>
@@ -53894,7 +53901,7 @@
         <v>2613</v>
       </c>
       <c r="D884" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E884" t="s">
         <v>100</v>
@@ -53944,7 +53951,7 @@
         <v>2617</v>
       </c>
       <c r="D885" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E885" t="s">
         <v>100</v>
@@ -53994,7 +54001,7 @@
         <v>2620</v>
       </c>
       <c r="D886" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E886" t="s">
         <v>100</v>
@@ -54044,7 +54051,7 @@
         <v>2623</v>
       </c>
       <c r="D887" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E887" t="s">
         <v>100</v>
@@ -54094,7 +54101,7 @@
         <v>2626</v>
       </c>
       <c r="D888" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E888" t="s">
         <v>100</v>
@@ -54144,7 +54151,7 @@
         <v>2629</v>
       </c>
       <c r="D889" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E889" t="s">
         <v>100</v>
@@ -54194,7 +54201,7 @@
         <v>2633</v>
       </c>
       <c r="D890" t="s">
-        <v>2565</v>
+        <v>100</v>
       </c>
       <c r="E890" t="s">
         <v>100</v>
@@ -54244,7 +54251,7 @@
         <v>2636</v>
       </c>
       <c r="D891" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E891" t="s">
         <v>2637</v>
@@ -54294,7 +54301,7 @@
         <v>2641</v>
       </c>
       <c r="D892" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E892" t="s">
         <v>2637</v>
@@ -54344,7 +54351,7 @@
         <v>2643</v>
       </c>
       <c r="D893" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E893" t="s">
         <v>2637</v>
@@ -54394,7 +54401,7 @@
         <v>2645</v>
       </c>
       <c r="D894" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E894" t="s">
         <v>2637</v>
@@ -54444,7 +54451,7 @@
         <v>2647</v>
       </c>
       <c r="D895" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E895" t="s">
         <v>2637</v>
@@ -54494,7 +54501,7 @@
         <v>2649</v>
       </c>
       <c r="D896" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E896" t="s">
         <v>2637</v>
@@ -54544,7 +54551,7 @@
         <v>2651</v>
       </c>
       <c r="D897" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E897" t="s">
         <v>2637</v>
@@ -54594,7 +54601,7 @@
         <v>2653</v>
       </c>
       <c r="D898" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E898" t="s">
         <v>2637</v>
@@ -54644,7 +54651,7 @@
         <v>2655</v>
       </c>
       <c r="D899" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E899" t="s">
         <v>2637</v>
@@ -54694,7 +54701,7 @@
         <v>2658</v>
       </c>
       <c r="D900" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E900" t="s">
         <v>2637</v>
@@ -54744,7 +54751,7 @@
         <v>2660</v>
       </c>
       <c r="D901" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E901" t="s">
         <v>2637</v>
@@ -54794,7 +54801,7 @@
         <v>2662</v>
       </c>
       <c r="D902" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E902" t="s">
         <v>2637</v>
@@ -54844,7 +54851,7 @@
         <v>2665</v>
       </c>
       <c r="D903" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E903" t="s">
         <v>2637</v>
@@ -54891,7 +54898,7 @@
         <v>2667</v>
       </c>
       <c r="D904" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E904" t="s">
         <v>2637</v>
@@ -54935,7 +54942,7 @@
         <v>2670</v>
       </c>
       <c r="D905" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E905" t="s">
         <v>2637</v>
@@ -54985,7 +54992,7 @@
         <v>2672</v>
       </c>
       <c r="D906" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E906" t="s">
         <v>2637</v>
@@ -55035,7 +55042,7 @@
         <v>2675</v>
       </c>
       <c r="D907" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E907" t="s">
         <v>2637</v>
@@ -55085,7 +55092,7 @@
         <v>2678</v>
       </c>
       <c r="D908" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E908" t="s">
         <v>2637</v>
@@ -55135,7 +55142,7 @@
         <v>2681</v>
       </c>
       <c r="D909" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E909" t="s">
         <v>2637</v>
@@ -55185,7 +55192,7 @@
         <v>2684</v>
       </c>
       <c r="D910" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E910" t="s">
         <v>2637</v>
@@ -55235,7 +55242,7 @@
         <v>2687</v>
       </c>
       <c r="D911" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E911" t="s">
         <v>2637</v>
@@ -55282,7 +55289,7 @@
         <v>2651</v>
       </c>
       <c r="D912" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E912" t="s">
         <v>2637</v>
@@ -55329,7 +55336,7 @@
         <v>2691</v>
       </c>
       <c r="D913" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E913" t="s">
         <v>2637</v>
@@ -55373,7 +55380,7 @@
         <v>2693</v>
       </c>
       <c r="D914" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E914" t="s">
         <v>2637</v>
@@ -55420,7 +55427,7 @@
         <v>2695</v>
       </c>
       <c r="D915" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E915" t="s">
         <v>2637</v>
@@ -55461,7 +55468,7 @@
         <v>2697</v>
       </c>
       <c r="D916" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E916" t="s">
         <v>2637</v>
@@ -55502,7 +55509,7 @@
         <v>2699</v>
       </c>
       <c r="D917" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E917" t="s">
         <v>2637</v>
@@ -55543,7 +55550,7 @@
         <v>2701</v>
       </c>
       <c r="D918" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E918" t="s">
         <v>2637</v>
@@ -55584,7 +55591,7 @@
         <v>2704</v>
       </c>
       <c r="D919" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E919" t="s">
         <v>2637</v>
@@ -55625,7 +55632,7 @@
         <v>2706</v>
       </c>
       <c r="D920" t="s">
-        <v>2565</v>
+        <v>2637</v>
       </c>
       <c r="E920" t="s">
         <v>2637</v>
@@ -55658,7 +55665,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="921" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
         <v>2707</v>
       </c>
@@ -55711,7 +55718,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="922" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
         <v>2712</v>
       </c>
@@ -55761,7 +55768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="923" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
         <v>2714</v>
       </c>
@@ -55814,7 +55821,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="924" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
         <v>2717</v>
       </c>
@@ -55864,7 +55871,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="925" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
         <v>2719</v>
       </c>
@@ -55917,7 +55924,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="926" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
         <v>2721</v>
       </c>
@@ -55967,7 +55974,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="927" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
         <v>2723</v>
       </c>
@@ -56020,7 +56027,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="928" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
         <v>2727</v>
       </c>
@@ -56073,7 +56080,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="929" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
         <v>2730</v>
       </c>
@@ -56126,7 +56133,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="930" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
         <v>2734</v>
       </c>
@@ -56179,7 +56186,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="931" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
         <v>2737</v>
       </c>
@@ -56232,7 +56239,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="932" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
         <v>2740</v>
       </c>
@@ -56282,7 +56289,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="933" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
         <v>2742</v>
       </c>
@@ -56332,7 +56339,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="934" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
         <v>2746</v>
       </c>
@@ -56382,7 +56389,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="935" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
         <v>2749</v>
       </c>
@@ -56435,7 +56442,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="936" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
         <v>2754</v>
       </c>
@@ -56488,7 +56495,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="937" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
         <v>2757</v>
       </c>
@@ -56541,7 +56548,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="938" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
         <v>2760</v>
       </c>
@@ -56594,7 +56601,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="939" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
         <v>2763</v>
       </c>
@@ -56647,7 +56654,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="940" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
         <v>2767</v>
       </c>
@@ -56700,7 +56707,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="941" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
         <v>2770</v>
       </c>
@@ -56753,7 +56760,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="942" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
         <v>2771</v>
       </c>
@@ -56803,7 +56810,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="943" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
         <v>2772</v>
       </c>
@@ -56856,7 +56863,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="944" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
         <v>2775</v>
       </c>
@@ -56906,7 +56913,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="945" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
         <v>2779</v>
       </c>
@@ -56956,7 +56963,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="946" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
         <v>2781</v>
       </c>
@@ -57006,7 +57013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="947" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
         <v>2785</v>
       </c>
@@ -57056,7 +57063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="948" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
         <v>2787</v>
       </c>
@@ -57106,7 +57113,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="949" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
         <v>2789</v>
       </c>
@@ -57156,7 +57163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="950" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
         <v>2791</v>
       </c>
@@ -57206,7 +57213,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="951" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
         <v>2793</v>
       </c>
@@ -57256,7 +57263,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="952" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
         <v>2795</v>
       </c>
@@ -57306,7 +57313,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="953" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
         <v>2797</v>
       </c>
@@ -57356,7 +57363,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="954" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
         <v>2799</v>
       </c>
@@ -57406,7 +57413,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="955" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
         <v>2801</v>
       </c>
@@ -57456,7 +57463,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="956" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
         <v>2803</v>
       </c>
@@ -57506,7 +57513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="957" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
         <v>2805</v>
       </c>
@@ -57556,7 +57563,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="958" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
         <v>2807</v>
       </c>
@@ -57606,7 +57613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="959" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
         <v>2809</v>
       </c>
@@ -57656,7 +57663,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="960" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
         <v>2811</v>
       </c>
@@ -57706,7 +57713,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="961" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
         <v>2813</v>
       </c>
@@ -57756,7 +57763,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="962" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
         <v>2815</v>
       </c>
@@ -57806,7 +57813,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="963" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
         <v>2817</v>
       </c>
@@ -57856,7 +57863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="964" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
         <v>2819</v>
       </c>
@@ -57903,7 +57910,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="965" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
         <v>2822</v>
       </c>
@@ -57950,7 +57957,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="966" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
         <v>2824</v>
       </c>
@@ -57997,7 +58004,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="967" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
         <v>2826</v>
       </c>
@@ -58044,7 +58051,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="968" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
         <v>2828</v>
       </c>
@@ -58091,7 +58098,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="969" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
         <v>2830</v>
       </c>
@@ -58141,7 +58148,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="970" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
         <v>2834</v>
       </c>
@@ -58191,7 +58198,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="971" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
         <v>2836</v>
       </c>
@@ -58241,7 +58248,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="972" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
         <v>2830</v>
       </c>
@@ -58291,7 +58298,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="973" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
         <v>2834</v>
       </c>
@@ -58341,7 +58348,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="974" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
         <v>2839</v>
       </c>
@@ -58391,7 +58398,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="975" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
         <v>2841</v>
       </c>
@@ -58441,7 +58448,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="976" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
         <v>2843</v>
       </c>
@@ -58491,7 +58498,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="977" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>2845</v>
       </c>
@@ -58541,7 +58548,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="978" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>2847</v>
       </c>
@@ -58591,7 +58598,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="979" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
         <v>2849</v>
       </c>
@@ -58641,7 +58648,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="980" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
         <v>2850</v>
       </c>
@@ -58691,7 +58698,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="981" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
         <v>2852</v>
       </c>
@@ -58741,7 +58748,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="982" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
         <v>2854</v>
       </c>
@@ -58791,7 +58798,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="983" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
         <v>2856</v>
       </c>
@@ -58841,7 +58848,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="984" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
         <v>2858</v>
       </c>
@@ -58891,7 +58898,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="985" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
         <v>2860</v>
       </c>
@@ -58941,7 +58948,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="986" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
         <v>2862</v>
       </c>
@@ -58991,7 +58998,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="987" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
         <v>2864</v>
       </c>
@@ -59041,7 +59048,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="988" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
         <v>2866</v>
       </c>
@@ -59091,7 +59098,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="989" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
         <v>2868</v>
       </c>
@@ -59141,7 +59148,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="990" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="990" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
         <v>2870</v>
       </c>
@@ -59191,7 +59198,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="991" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
         <v>2872</v>
       </c>
@@ -59241,7 +59248,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="992" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
         <v>2874</v>
       </c>
@@ -59291,7 +59298,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="993" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
         <v>2876</v>
       </c>
@@ -59341,7 +59348,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="994" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
         <v>2878</v>
       </c>
@@ -59391,7 +59398,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="995" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
         <v>2880</v>
       </c>
@@ -59441,7 +59448,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="996" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
         <v>2885</v>
       </c>
@@ -59494,7 +59501,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="997" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
         <v>2888</v>
       </c>
@@ -59547,7 +59554,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="998" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
         <v>2890</v>
       </c>
@@ -59600,7 +59607,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="999" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="999" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
         <v>2893</v>
       </c>
@@ -59650,7 +59657,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1000" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
         <v>2896</v>
       </c>
@@ -59700,7 +59707,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1001" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1001" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
         <v>2899</v>
       </c>
@@ -59750,7 +59757,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1002" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1002" t="s">
         <v>2902</v>
       </c>
@@ -59803,7 +59810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1003" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1003" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1003" t="s">
         <v>2907</v>
       </c>
@@ -59856,7 +59863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1004" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1004" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1004" t="s">
         <v>2910</v>
       </c>
@@ -59909,7 +59916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1005" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1005" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1005" t="s">
         <v>2913</v>
       </c>
@@ -59962,7 +59969,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1006" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1006" t="s">
         <v>2916</v>
       </c>
@@ -60015,7 +60022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1007" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1007" t="s">
         <v>2919</v>
       </c>
@@ -60065,7 +60072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1008" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1008" t="s">
         <v>2920</v>
       </c>
@@ -60115,7 +60122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1009" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1009" t="s">
         <v>2922</v>
       </c>
@@ -60168,7 +60175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1010" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1010" t="s">
         <v>2925</v>
       </c>
@@ -60221,7 +60228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1011" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1011" t="s">
         <v>2928</v>
       </c>
@@ -60274,7 +60281,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1012" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1012" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1012" t="s">
         <v>2931</v>
       </c>
@@ -60327,7 +60334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1013" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1013" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1013" t="s">
         <v>2934</v>
       </c>
@@ -60380,7 +60387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1014" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1014" t="s">
         <v>2935</v>
       </c>
@@ -60430,7 +60437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1015" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1015" t="s">
         <v>2936</v>
       </c>
@@ -60483,7 +60490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1016" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1016" t="s">
         <v>2939</v>
       </c>
@@ -60536,7 +60543,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1017" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1017" t="s">
         <v>2942</v>
       </c>
@@ -60589,7 +60596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1018" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1018" t="s">
         <v>2945</v>
       </c>
@@ -60642,7 +60649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1019" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1019" t="s">
         <v>2946</v>
       </c>
@@ -60692,7 +60699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1020" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1020" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1020" t="s">
         <v>2947</v>
       </c>
@@ -60742,7 +60749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1021" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1021" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1021" t="s">
         <v>2948</v>
       </c>
@@ -60792,7 +60799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1022" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1022" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1022" t="s">
         <v>2950</v>
       </c>
@@ -60842,7 +60849,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="1023" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1023" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1023" t="s">
         <v>2952</v>
       </c>
@@ -60895,7 +60902,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1024" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1024" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1024" t="s">
         <v>2956</v>
       </c>
@@ -60948,7 +60955,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1025" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1025" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1025" t="s">
         <v>2959</v>
       </c>
@@ -61001,7 +61008,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1026" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1026" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1026" t="s">
         <v>2962</v>
       </c>
@@ -61054,7 +61061,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1027" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1027" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1027" t="s">
         <v>2965</v>
       </c>
@@ -61104,7 +61111,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1028" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1028" t="s">
         <v>2966</v>
       </c>
@@ -61154,7 +61161,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1029" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1029" t="s">
         <v>2969</v>
       </c>
@@ -61207,7 +61214,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1030" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1030" t="s">
         <v>2973</v>
       </c>
@@ -61260,7 +61267,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1031" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1031" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1031" t="s">
         <v>2976</v>
       </c>
@@ -61313,7 +61320,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1032" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1032" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1032" t="s">
         <v>2979</v>
       </c>
@@ -61363,7 +61370,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1033" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1033" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1033" t="s">
         <v>2980</v>
       </c>
@@ -61413,7 +61420,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1034" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1034" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1034" t="s">
         <v>2982</v>
       </c>
@@ -61463,7 +61470,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1035" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1035" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1035" t="s">
         <v>2983</v>
       </c>
@@ -61516,7 +61523,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="1036" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1036" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1036" t="s">
         <v>2986</v>
       </c>
@@ -61569,7 +61576,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1037" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1037" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1037" t="s">
         <v>2990</v>
       </c>
@@ -61622,7 +61629,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1038" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1038" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
         <v>2993</v>
       </c>
@@ -61672,7 +61679,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1039" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1039" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
         <v>2994</v>
       </c>
@@ -61722,7 +61729,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1040" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1040" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
         <v>2995</v>
       </c>
@@ -61775,7 +61782,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1041" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
         <v>2998</v>
       </c>
@@ -61825,7 +61832,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1042" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
         <v>2999</v>
       </c>
@@ -61878,7 +61885,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1043" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
         <v>3001</v>
       </c>
@@ -61928,7 +61935,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1044" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
         <v>3002</v>
       </c>
@@ -61978,7 +61985,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1045" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
         <v>3003</v>
       </c>
@@ -62028,7 +62035,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1046" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
         <v>3004</v>
       </c>
@@ -62081,7 +62088,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1047" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1047" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
         <v>3007</v>
       </c>
@@ -62134,7 +62141,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1048" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1048" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
         <v>3010</v>
       </c>
@@ -62184,7 +62191,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1049" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1049" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
         <v>3011</v>
       </c>
@@ -62234,7 +62241,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1050" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
         <v>3012</v>
       </c>
@@ -62284,7 +62291,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1051" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
         <v>3013</v>
       </c>
@@ -62334,7 +62341,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1052" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
         <v>3014</v>
       </c>
@@ -62384,7 +62391,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1053" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1053" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
         <v>3016</v>
       </c>
@@ -62434,7 +62441,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1054" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
         <v>3017</v>
       </c>
@@ -62484,7 +62491,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1055" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1055" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
         <v>3018</v>
       </c>
@@ -62534,7 +62541,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1056" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
         <v>3019</v>
       </c>
@@ -62584,7 +62591,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1057" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
         <v>3021</v>
       </c>
@@ -62634,7 +62641,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1058" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1058" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
         <v>3023</v>
       </c>
@@ -62687,7 +62694,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="1059" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1059" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
         <v>3027</v>
       </c>
@@ -62740,7 +62747,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1060" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1060" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
         <v>3030</v>
       </c>
@@ -62793,7 +62800,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1061" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1061" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
         <v>3033</v>
       </c>
@@ -62846,7 +62853,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1062" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1062" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
         <v>3036</v>
       </c>
@@ -62899,7 +62906,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1063" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1063" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
         <v>3039</v>
       </c>
@@ -62952,7 +62959,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1064" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
         <v>3042</v>
       </c>
@@ -63002,7 +63009,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1065" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1065" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
         <v>3043</v>
       </c>
@@ -63052,7 +63059,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1066" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1066" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
         <v>3045</v>
       </c>
@@ -63102,7 +63109,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1067" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1067" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
         <v>3047</v>
       </c>
@@ -63152,7 +63159,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1068" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
         <v>3049</v>
       </c>
@@ -63202,7 +63209,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1069" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1069" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
         <v>3047</v>
       </c>
@@ -63252,7 +63259,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1070" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1070" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
         <v>3050</v>
       </c>
@@ -63302,7 +63309,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1071" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1071" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
         <v>3051</v>
       </c>
@@ -63352,7 +63359,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1072" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1072" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
         <v>3052</v>
       </c>
@@ -63402,7 +63409,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1073" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1073" t="s">
         <v>3053</v>
       </c>
@@ -63452,7 +63459,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="1074" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1074" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1074" t="s">
         <v>3055</v>
       </c>

--- a/templates/stock_template.xlsx
+++ b/templates/stock_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nan2.shao\Desktop\Inventory\0814\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B75A69-24E1-4239-8D5C-1FCD31B8CE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D529A775-0D8F-488A-90E3-915B7A7E6776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="752" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14105" uniqueCount="3072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14105" uniqueCount="3073">
   <si>
     <t>SKU no.</t>
   </si>
@@ -8392,9 +8392,6 @@
   </si>
   <si>
     <t>HSM-NT48-HH455</t>
-  </si>
-  <si>
-    <t>T5 PRO</t>
   </si>
   <si>
     <t>T5 Pro-48</t>
@@ -9264,6 +9261,14 @@
   </si>
   <si>
     <t>BLUEARKX5 50K-100</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>T5 Pro-60</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>T5 Pro-66</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -9443,12 +9448,7 @@
   <autoFilter ref="A1:Q1074" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="3">
       <filters>
-        <filter val="Cells"/>
-        <filter val="Drive"/>
-        <filter val="Heat Pump"/>
-        <filter val="MI"/>
-        <filter val="Non-PV"/>
-        <filter val="Reserve"/>
+        <filter val="T5 PRO"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9858,10 +9858,10 @@
     </row>
     <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C2" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="D2" t="s">
         <v>2709</v>
@@ -9882,22 +9882,22 @@
         <v>864</v>
       </c>
       <c r="J2" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="K2" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="L2" t="s">
         <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="N2">
         <v>445</v>
       </c>
       <c r="O2" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="P2" t="s">
         <v>2710</v>
@@ -9906,12 +9906,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="C3" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="D3" t="s">
         <v>2637</v>
@@ -9923,7 +9923,7 @@
         <v>2566</v>
       </c>
       <c r="G3" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="J3" t="s">
         <v>2668</v>
@@ -9935,7 +9935,7 @@
         <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="O3" t="s">
         <v>105</v>
@@ -9947,12 +9947,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C4" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="D4" t="s">
         <v>2637</v>
@@ -9964,7 +9964,7 @@
         <v>2566</v>
       </c>
       <c r="G4" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="J4" t="s">
         <v>2668</v>
@@ -9976,10 +9976,10 @@
         <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="O4" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="P4" t="s">
         <v>2566</v>
@@ -9990,16 +9990,16 @@
     </row>
     <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C5" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="D5" t="s">
         <v>2709</v>
       </c>
       <c r="E5" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -10014,25 +10014,25 @@
         <v>594</v>
       </c>
       <c r="J5" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="K5" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="N5">
         <v>715</v>
       </c>
       <c r="O5" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="P5" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="Q5" t="s">
         <v>152</v>
@@ -10040,16 +10040,16 @@
     </row>
     <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C6" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="D6" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E6" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -10064,25 +10064,25 @@
         <v>594</v>
       </c>
       <c r="J6" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="K6" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="N6">
         <v>720</v>
       </c>
       <c r="O6" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="P6" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q6" t="s">
         <v>152</v>
@@ -10090,16 +10090,16 @@
     </row>
     <row r="7" spans="1:17" ht="15" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
+        <v>3055</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>3056</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3057</v>
       </c>
       <c r="D7" t="s">
         <v>2709</v>
       </c>
       <c r="E7" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -10114,16 +10114,16 @@
         <v>720</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="N7">
         <v>585</v>
@@ -10132,7 +10132,7 @@
         <v>23</v>
       </c>
       <c r="P7" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="Q7" t="s">
         <v>152</v>
@@ -10435,7 +10435,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -10576,7 +10576,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -10717,7 +10717,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -10905,7 +10905,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>72</v>
       </c>
@@ -11140,7 +11140,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -11187,7 +11187,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>79</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>81</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>85</v>
       </c>
@@ -11375,7 +11375,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>87</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>89</v>
       </c>
@@ -11469,7 +11469,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>97</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>106</v>
       </c>
@@ -11616,7 +11616,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -13111,7 +13111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>193</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>198</v>
       </c>
@@ -13211,7 +13211,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>200</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>203</v>
       </c>
@@ -13311,7 +13311,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>206</v>
       </c>
@@ -13361,7 +13361,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>209</v>
       </c>
@@ -13411,7 +13411,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>212</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>215</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>218</v>
       </c>
@@ -37461,7 +37461,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="555" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1619</v>
       </c>
@@ -37508,7 +37508,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="556" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1624</v>
       </c>
@@ -37558,7 +37558,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="557" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>1627</v>
       </c>
@@ -37605,7 +37605,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="558" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1630</v>
       </c>
@@ -37652,7 +37652,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="559" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1634</v>
       </c>
@@ -37699,7 +37699,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="560" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1639</v>
       </c>
@@ -37746,7 +37746,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="561" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>1642</v>
       </c>
@@ -37793,7 +37793,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="562" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1644</v>
       </c>
@@ -37840,7 +37840,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="563" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>1646</v>
       </c>
@@ -37887,7 +37887,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="564" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1648</v>
       </c>
@@ -37934,7 +37934,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="565" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>1650</v>
       </c>
@@ -37981,7 +37981,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="566" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>1652</v>
       </c>
@@ -38028,7 +38028,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="567" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>1654</v>
       </c>
@@ -38075,7 +38075,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="568" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>1656</v>
       </c>
@@ -38122,7 +38122,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="569" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>1658</v>
       </c>
@@ -38169,7 +38169,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="570" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>1660</v>
       </c>
@@ -38216,7 +38216,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="571" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>1662</v>
       </c>
@@ -38263,7 +38263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="572" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>1664</v>
       </c>
@@ -38310,7 +38310,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="573" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>1666</v>
       </c>
@@ -38357,7 +38357,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="574" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>1668</v>
       </c>
@@ -38404,7 +38404,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="575" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>1670</v>
       </c>
@@ -38451,7 +38451,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="576" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>1672</v>
       </c>
@@ -38498,7 +38498,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="577" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>1674</v>
       </c>
@@ -38545,7 +38545,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="578" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>1676</v>
       </c>
@@ -38592,7 +38592,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="579" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>1678</v>
       </c>
@@ -38639,7 +38639,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="580" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>1680</v>
       </c>
@@ -38686,7 +38686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="581" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>1682</v>
       </c>
@@ -38736,7 +38736,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="582" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1684</v>
       </c>
@@ -38786,7 +38786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="583" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>1686</v>
       </c>
@@ -38836,7 +38836,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="584" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>1688</v>
       </c>
@@ -38886,7 +38886,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="585" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>1690</v>
       </c>
@@ -38936,7 +38936,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="586" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>1692</v>
       </c>
@@ -38983,7 +38983,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="587" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>1696</v>
       </c>
@@ -39030,7 +39030,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="588" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>1698</v>
       </c>
@@ -39077,7 +39077,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="589" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1700</v>
       </c>
@@ -39124,7 +39124,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="590" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>1702</v>
       </c>
@@ -39171,7 +39171,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="591" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>1704</v>
       </c>
@@ -39218,7 +39218,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="592" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>1706</v>
       </c>
@@ -39265,7 +39265,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="593" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>1708</v>
       </c>
@@ -39312,7 +39312,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="594" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>1710</v>
       </c>
@@ -39359,7 +39359,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="595" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1712</v>
       </c>
@@ -39406,7 +39406,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="596" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>1714</v>
       </c>
@@ -39453,7 +39453,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="597" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1716</v>
       </c>
@@ -39500,7 +39500,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="598" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1718</v>
       </c>
@@ -39547,7 +39547,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="599" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1720</v>
       </c>
@@ -53140,7 +53140,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="869" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>2563</v>
       </c>
@@ -53190,7 +53190,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="870" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>2569</v>
       </c>
@@ -53240,7 +53240,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="871" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>2572</v>
       </c>
@@ -53290,7 +53290,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="872" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>2575</v>
       </c>
@@ -53340,7 +53340,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="873" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>2578</v>
       </c>
@@ -53390,7 +53390,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="874" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>2581</v>
       </c>
@@ -53440,7 +53440,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="875" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>2585</v>
       </c>
@@ -53490,7 +53490,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="876" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>2587</v>
       </c>
@@ -53540,7 +53540,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="877" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>2590</v>
       </c>
@@ -53590,7 +53590,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="878" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>2593</v>
       </c>
@@ -53640,7 +53640,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="879" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>2596</v>
       </c>
@@ -53690,7 +53690,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="880" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>2599</v>
       </c>
@@ -53740,7 +53740,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="881" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>2602</v>
       </c>
@@ -53790,7 +53790,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="882" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>2604</v>
       </c>
@@ -53840,7 +53840,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="883" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>2607</v>
       </c>
@@ -53890,7 +53890,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="884" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>2612</v>
       </c>
@@ -53940,7 +53940,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="885" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>2616</v>
       </c>
@@ -53990,7 +53990,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="886" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>2619</v>
       </c>
@@ -54040,7 +54040,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="887" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>2622</v>
       </c>
@@ -54090,7 +54090,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="888" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>2625</v>
       </c>
@@ -54140,7 +54140,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="889" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>2628</v>
       </c>
@@ -54190,7 +54190,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="890" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>2632</v>
       </c>
@@ -54240,7 +54240,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="891" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>2635</v>
       </c>
@@ -54290,7 +54290,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="892" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>2640</v>
       </c>
@@ -54340,7 +54340,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="893" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>2642</v>
       </c>
@@ -54390,7 +54390,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="894" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>2644</v>
       </c>
@@ -54440,7 +54440,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="895" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>2646</v>
       </c>
@@ -54490,7 +54490,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="896" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>2648</v>
       </c>
@@ -54540,7 +54540,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="897" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>2650</v>
       </c>
@@ -54590,7 +54590,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="898" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>2652</v>
       </c>
@@ -54640,7 +54640,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="899" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>2654</v>
       </c>
@@ -54690,7 +54690,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="900" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>2657</v>
       </c>
@@ -54740,7 +54740,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="901" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>2659</v>
       </c>
@@ -54790,7 +54790,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="902" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>2661</v>
       </c>
@@ -54840,7 +54840,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="903" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>2664</v>
       </c>
@@ -54890,7 +54890,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="904" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>2666</v>
       </c>
@@ -54931,7 +54931,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="905" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>2669</v>
       </c>
@@ -54981,7 +54981,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="906" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>2671</v>
       </c>
@@ -55031,7 +55031,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="907" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>2674</v>
       </c>
@@ -55081,7 +55081,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="908" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>2677</v>
       </c>
@@ -55131,7 +55131,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="909" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>2680</v>
       </c>
@@ -55181,7 +55181,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="910" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>2683</v>
       </c>
@@ -55231,7 +55231,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="911" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>2686</v>
       </c>
@@ -55281,7 +55281,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="912" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>2689</v>
       </c>
@@ -55328,7 +55328,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="913" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
         <v>2690</v>
       </c>
@@ -55372,7 +55372,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="914" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
         <v>2692</v>
       </c>
@@ -55419,7 +55419,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="915" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
         <v>2694</v>
       </c>
@@ -55460,7 +55460,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="916" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
         <v>2696</v>
       </c>
@@ -55501,7 +55501,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="917" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
         <v>2698</v>
       </c>
@@ -55542,7 +55542,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="918" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
         <v>2700</v>
       </c>
@@ -55583,7 +55583,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="919" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
         <v>2703</v>
       </c>
@@ -55624,7 +55624,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="920" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
         <v>2705</v>
       </c>
@@ -56963,7 +56963,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="946" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
         <v>2781</v>
       </c>
@@ -56971,10 +56971,10 @@
         <v>2782</v>
       </c>
       <c r="D946" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E946" t="s">
         <v>2783</v>
-      </c>
-      <c r="E946" t="s">
-        <v>2784</v>
       </c>
       <c r="F946" t="s">
         <v>21</v>
@@ -57007,24 +57007,24 @@
         <v>23</v>
       </c>
       <c r="P946" t="s">
+        <v>2783</v>
+      </c>
+      <c r="Q946" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="947" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A947" t="s">
         <v>2784</v>
       </c>
-      <c r="Q946" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="947" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A947" t="s">
+      <c r="C947" t="s">
         <v>2785</v>
       </c>
-      <c r="C947" t="s">
-        <v>2786</v>
-      </c>
       <c r="D947" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E947" t="s">
         <v>2783</v>
-      </c>
-      <c r="E947" t="s">
-        <v>2784</v>
       </c>
       <c r="F947" t="s">
         <v>21</v>
@@ -57039,16 +57039,16 @@
         <v>936</v>
       </c>
       <c r="J947" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="K947" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="L947" t="s">
         <v>23</v>
       </c>
       <c r="M947" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="N947">
         <v>460</v>
@@ -57057,24 +57057,24 @@
         <v>23</v>
       </c>
       <c r="P947" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q947" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="948" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C948" t="s">
         <v>2787</v>
       </c>
-      <c r="C948" t="s">
-        <v>2788</v>
-      </c>
       <c r="D948" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E948" t="s">
         <v>2783</v>
-      </c>
-      <c r="E948" t="s">
-        <v>2784</v>
       </c>
       <c r="F948" t="s">
         <v>21</v>
@@ -57089,16 +57089,16 @@
         <v>936</v>
       </c>
       <c r="J948" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="K948" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="L948" t="s">
         <v>23</v>
       </c>
       <c r="M948" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="N948">
         <v>465</v>
@@ -57107,24 +57107,24 @@
         <v>23</v>
       </c>
       <c r="P948" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q948" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="949" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C949" t="s">
         <v>2789</v>
       </c>
-      <c r="C949" t="s">
-        <v>2790</v>
-      </c>
       <c r="D949" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E949" t="s">
         <v>2783</v>
-      </c>
-      <c r="E949" t="s">
-        <v>2784</v>
       </c>
       <c r="F949" t="s">
         <v>21</v>
@@ -57139,16 +57139,16 @@
         <v>936</v>
       </c>
       <c r="J949" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="K949" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="L949" t="s">
         <v>23</v>
       </c>
       <c r="M949" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="N949">
         <v>470</v>
@@ -57157,24 +57157,24 @@
         <v>23</v>
       </c>
       <c r="P949" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q949" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="950" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C950" t="s">
         <v>2791</v>
       </c>
-      <c r="C950" t="s">
-        <v>2792</v>
-      </c>
       <c r="D950" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E950" t="s">
         <v>2783</v>
-      </c>
-      <c r="E950" t="s">
-        <v>2784</v>
       </c>
       <c r="F950" t="s">
         <v>21</v>
@@ -57189,16 +57189,16 @@
         <v>936</v>
       </c>
       <c r="J950" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="K950" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="L950" t="s">
         <v>23</v>
       </c>
       <c r="M950" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="N950">
         <v>475</v>
@@ -57207,24 +57207,24 @@
         <v>23</v>
       </c>
       <c r="P950" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q950" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="951" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C951" t="s">
         <v>2793</v>
       </c>
-      <c r="C951" t="s">
-        <v>2794</v>
-      </c>
       <c r="D951" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E951" t="s">
         <v>2783</v>
-      </c>
-      <c r="E951" t="s">
-        <v>2784</v>
       </c>
       <c r="F951" t="s">
         <v>21</v>
@@ -57239,16 +57239,16 @@
         <v>936</v>
       </c>
       <c r="J951" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="K951" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="L951" t="s">
         <v>23</v>
       </c>
       <c r="M951" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="N951">
         <v>450</v>
@@ -57257,24 +57257,24 @@
         <v>23</v>
       </c>
       <c r="P951" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q951" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="952" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C952" t="s">
         <v>2795</v>
       </c>
-      <c r="C952" t="s">
-        <v>2796</v>
-      </c>
       <c r="D952" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E952" t="s">
         <v>2783</v>
-      </c>
-      <c r="E952" t="s">
-        <v>2784</v>
       </c>
       <c r="F952" t="s">
         <v>21</v>
@@ -57289,16 +57289,16 @@
         <v>936</v>
       </c>
       <c r="J952" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="K952" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="L952" t="s">
         <v>23</v>
       </c>
       <c r="M952" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
       <c r="N952">
         <v>455</v>
@@ -57307,24 +57307,24 @@
         <v>23</v>
       </c>
       <c r="P952" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q952" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="953" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C953" t="s">
         <v>2797</v>
       </c>
-      <c r="C953" t="s">
-        <v>2798</v>
-      </c>
       <c r="D953" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E953" t="s">
         <v>2783</v>
-      </c>
-      <c r="E953" t="s">
-        <v>2784</v>
       </c>
       <c r="F953" t="s">
         <v>21</v>
@@ -57339,16 +57339,16 @@
         <v>936</v>
       </c>
       <c r="J953" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="K953" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="L953" t="s">
         <v>23</v>
       </c>
       <c r="M953" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="N953">
         <v>460</v>
@@ -57357,24 +57357,24 @@
         <v>23</v>
       </c>
       <c r="P953" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q953" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="954" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C954" t="s">
         <v>2799</v>
       </c>
-      <c r="C954" t="s">
-        <v>2800</v>
-      </c>
       <c r="D954" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E954" t="s">
         <v>2783</v>
-      </c>
-      <c r="E954" t="s">
-        <v>2784</v>
       </c>
       <c r="F954" t="s">
         <v>21</v>
@@ -57389,16 +57389,16 @@
         <v>936</v>
       </c>
       <c r="J954" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="K954" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="L954" t="s">
         <v>23</v>
       </c>
       <c r="M954" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="N954">
         <v>465</v>
@@ -57407,24 +57407,24 @@
         <v>23</v>
       </c>
       <c r="P954" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q954" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="955" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C955" t="s">
         <v>2801</v>
       </c>
-      <c r="C955" t="s">
-        <v>2802</v>
-      </c>
       <c r="D955" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E955" t="s">
         <v>2783</v>
-      </c>
-      <c r="E955" t="s">
-        <v>2784</v>
       </c>
       <c r="F955" t="s">
         <v>21</v>
@@ -57439,16 +57439,16 @@
         <v>936</v>
       </c>
       <c r="J955" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="K955" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="L955" t="s">
         <v>23</v>
       </c>
       <c r="M955" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="N955">
         <v>470</v>
@@ -57457,24 +57457,24 @@
         <v>23</v>
       </c>
       <c r="P955" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q955" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="956" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C956" t="s">
         <v>2803</v>
       </c>
-      <c r="C956" t="s">
-        <v>2804</v>
-      </c>
       <c r="D956" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E956" t="s">
         <v>2783</v>
-      </c>
-      <c r="E956" t="s">
-        <v>2784</v>
       </c>
       <c r="F956" t="s">
         <v>21</v>
@@ -57489,16 +57489,16 @@
         <v>936</v>
       </c>
       <c r="J956" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="K956" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="L956" t="s">
         <v>23</v>
       </c>
       <c r="M956" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="N956">
         <v>475</v>
@@ -57507,24 +57507,24 @@
         <v>23</v>
       </c>
       <c r="P956" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q956" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="957" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C957" t="s">
         <v>2805</v>
       </c>
-      <c r="C957" t="s">
-        <v>2806</v>
-      </c>
       <c r="D957" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E957" t="s">
         <v>2783</v>
-      </c>
-      <c r="E957" t="s">
-        <v>2784</v>
       </c>
       <c r="F957" t="s">
         <v>21</v>
@@ -57539,16 +57539,16 @@
         <v>936</v>
       </c>
       <c r="J957" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="K957" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="L957" t="s">
         <v>23</v>
       </c>
       <c r="M957" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="N957">
         <v>480</v>
@@ -57557,24 +57557,24 @@
         <v>23</v>
       </c>
       <c r="P957" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q957" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="958" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
+        <v>2806</v>
+      </c>
+      <c r="C958" t="s">
         <v>2807</v>
       </c>
-      <c r="C958" t="s">
-        <v>2808</v>
-      </c>
       <c r="D958" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E958" t="s">
         <v>2783</v>
-      </c>
-      <c r="E958" t="s">
-        <v>2784</v>
       </c>
       <c r="F958" t="s">
         <v>21</v>
@@ -57589,16 +57589,16 @@
         <v>936</v>
       </c>
       <c r="J958" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="K958" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="L958" t="s">
         <v>23</v>
       </c>
       <c r="M958" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="N958">
         <v>455</v>
@@ -57607,24 +57607,24 @@
         <v>23</v>
       </c>
       <c r="P958" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q958" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="959" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C959" t="s">
         <v>2809</v>
       </c>
-      <c r="C959" t="s">
-        <v>2810</v>
-      </c>
       <c r="D959" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E959" t="s">
         <v>2783</v>
-      </c>
-      <c r="E959" t="s">
-        <v>2784</v>
       </c>
       <c r="F959" t="s">
         <v>21</v>
@@ -57639,16 +57639,16 @@
         <v>936</v>
       </c>
       <c r="J959" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="K959" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="L959" t="s">
         <v>23</v>
       </c>
       <c r="M959" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="N959">
         <v>460</v>
@@ -57657,24 +57657,24 @@
         <v>23</v>
       </c>
       <c r="P959" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q959" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="960" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C960" t="s">
         <v>2811</v>
       </c>
-      <c r="C960" t="s">
-        <v>2812</v>
-      </c>
       <c r="D960" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E960" t="s">
         <v>2783</v>
-      </c>
-      <c r="E960" t="s">
-        <v>2784</v>
       </c>
       <c r="F960" t="s">
         <v>21</v>
@@ -57689,16 +57689,16 @@
         <v>936</v>
       </c>
       <c r="J960" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="K960" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="L960" t="s">
         <v>23</v>
       </c>
       <c r="M960" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="N960">
         <v>465</v>
@@ -57707,24 +57707,24 @@
         <v>23</v>
       </c>
       <c r="P960" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q960" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="961" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C961" t="s">
         <v>2813</v>
       </c>
-      <c r="C961" t="s">
-        <v>2814</v>
-      </c>
       <c r="D961" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E961" t="s">
         <v>2783</v>
-      </c>
-      <c r="E961" t="s">
-        <v>2784</v>
       </c>
       <c r="F961" t="s">
         <v>21</v>
@@ -57739,16 +57739,16 @@
         <v>936</v>
       </c>
       <c r="J961" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="K961" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="L961" t="s">
         <v>23</v>
       </c>
       <c r="M961" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="N961">
         <v>470</v>
@@ -57757,24 +57757,24 @@
         <v>23</v>
       </c>
       <c r="P961" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q961" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="962" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C962" t="s">
         <v>2815</v>
       </c>
-      <c r="C962" t="s">
-        <v>2816</v>
-      </c>
       <c r="D962" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E962" t="s">
         <v>2783</v>
-      </c>
-      <c r="E962" t="s">
-        <v>2784</v>
       </c>
       <c r="F962" t="s">
         <v>21</v>
@@ -57789,16 +57789,16 @@
         <v>936</v>
       </c>
       <c r="J962" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="K962" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="L962" t="s">
         <v>23</v>
       </c>
       <c r="M962" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="N962">
         <v>475</v>
@@ -57807,24 +57807,24 @@
         <v>23</v>
       </c>
       <c r="P962" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q962" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="963" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C963" t="s">
         <v>2817</v>
       </c>
-      <c r="C963" t="s">
-        <v>2818</v>
-      </c>
       <c r="D963" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E963" t="s">
         <v>2783</v>
-      </c>
-      <c r="E963" t="s">
-        <v>2784</v>
       </c>
       <c r="F963" t="s">
         <v>21</v>
@@ -57839,16 +57839,16 @@
         <v>936</v>
       </c>
       <c r="J963" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="K963" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="L963" t="s">
         <v>23</v>
       </c>
       <c r="M963" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
       <c r="N963">
         <v>480</v>
@@ -57857,24 +57857,24 @@
         <v>23</v>
       </c>
       <c r="P963" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="Q963" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="964" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C964" t="s">
         <v>2819</v>
       </c>
-      <c r="C964" t="s">
-        <v>2820</v>
-      </c>
       <c r="D964" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E964" t="s">
-        <v>2821</v>
+        <v>3071</v>
       </c>
       <c r="F964" t="s">
         <v>21</v>
@@ -57886,16 +57886,16 @@
         <v>565</v>
       </c>
       <c r="J964" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="K964" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="L964" t="s">
         <v>23</v>
       </c>
       <c r="M964" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="N964">
         <v>565</v>
@@ -57904,24 +57904,24 @@
         <v>23</v>
       </c>
       <c r="P964" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="Q964" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="965" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
+        <v>2821</v>
+      </c>
+      <c r="C965" t="s">
         <v>2822</v>
       </c>
-      <c r="C965" t="s">
-        <v>2823</v>
-      </c>
       <c r="D965" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E965" t="s">
-        <v>2821</v>
+        <v>3071</v>
       </c>
       <c r="F965" t="s">
         <v>21</v>
@@ -57933,16 +57933,16 @@
         <v>570</v>
       </c>
       <c r="J965" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="K965" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="L965" t="s">
         <v>23</v>
       </c>
       <c r="M965" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="N965">
         <v>570</v>
@@ -57951,24 +57951,24 @@
         <v>23</v>
       </c>
       <c r="P965" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="Q965" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="966" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C966" t="s">
         <v>2824</v>
       </c>
-      <c r="C966" t="s">
-        <v>2825</v>
-      </c>
       <c r="D966" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E966" t="s">
-        <v>2821</v>
+        <v>3071</v>
       </c>
       <c r="F966" t="s">
         <v>21</v>
@@ -57980,16 +57980,16 @@
         <v>575</v>
       </c>
       <c r="J966" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="K966" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="L966" t="s">
         <v>23</v>
       </c>
       <c r="M966" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="N966">
         <v>575</v>
@@ -57998,24 +57998,24 @@
         <v>23</v>
       </c>
       <c r="P966" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="Q966" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="967" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="967" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
+        <v>2825</v>
+      </c>
+      <c r="C967" t="s">
         <v>2826</v>
       </c>
-      <c r="C967" t="s">
-        <v>2827</v>
-      </c>
       <c r="D967" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E967" t="s">
-        <v>2821</v>
+        <v>3071</v>
       </c>
       <c r="F967" t="s">
         <v>21</v>
@@ -58027,16 +58027,16 @@
         <v>580</v>
       </c>
       <c r="J967" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="K967" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="L967" t="s">
         <v>23</v>
       </c>
       <c r="M967" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="N967">
         <v>580</v>
@@ -58045,24 +58045,24 @@
         <v>23</v>
       </c>
       <c r="P967" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="Q967" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="968" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
+        <v>2827</v>
+      </c>
+      <c r="C968" t="s">
         <v>2828</v>
       </c>
-      <c r="C968" t="s">
-        <v>2829</v>
-      </c>
       <c r="D968" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E968" t="s">
-        <v>2821</v>
+        <v>3071</v>
       </c>
       <c r="F968" t="s">
         <v>21</v>
@@ -58074,16 +58074,16 @@
         <v>585</v>
       </c>
       <c r="J968" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="K968" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="L968" t="s">
         <v>23</v>
       </c>
       <c r="M968" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="N968">
         <v>585</v>
@@ -58092,24 +58092,24 @@
         <v>23</v>
       </c>
       <c r="P968" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="Q968" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="969" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C969" t="s">
         <v>2830</v>
       </c>
-      <c r="C969" t="s">
+      <c r="D969" t="s">
         <v>2831</v>
       </c>
-      <c r="D969" t="s">
+      <c r="E969" t="s">
         <v>2832</v>
-      </c>
-      <c r="E969" t="s">
-        <v>2833</v>
       </c>
       <c r="F969" t="s">
         <v>21</v>
@@ -58124,16 +58124,16 @@
         <v>720</v>
       </c>
       <c r="J969" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="K969" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="L969" t="s">
         <v>23</v>
       </c>
       <c r="M969" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="N969">
         <v>640</v>
@@ -58142,24 +58142,24 @@
         <v>23</v>
       </c>
       <c r="P969" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="Q969" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="970" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C970" t="s">
         <v>2834</v>
       </c>
-      <c r="C970" t="s">
-        <v>2835</v>
-      </c>
       <c r="D970" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E970" t="s">
         <v>2832</v>
-      </c>
-      <c r="E970" t="s">
-        <v>2833</v>
       </c>
       <c r="F970" t="s">
         <v>21</v>
@@ -58174,16 +58174,16 @@
         <v>720</v>
       </c>
       <c r="J970" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="K970" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="L970" t="s">
         <v>23</v>
       </c>
       <c r="M970" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="N970">
         <v>645</v>
@@ -58192,24 +58192,24 @@
         <v>23</v>
       </c>
       <c r="P970" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="Q970" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="971" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C971" t="s">
         <v>2836</v>
       </c>
-      <c r="C971" t="s">
-        <v>2837</v>
-      </c>
       <c r="D971" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E971" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F971" t="s">
         <v>21</v>
@@ -58224,16 +58224,16 @@
         <v>720</v>
       </c>
       <c r="J971" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="K971" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="L971" t="s">
         <v>23</v>
       </c>
       <c r="M971" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="N971">
         <v>635</v>
@@ -58242,24 +58242,24 @@
         <v>23</v>
       </c>
       <c r="P971" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q971" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="972" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C972" t="s">
         <v>2830</v>
       </c>
-      <c r="C972" t="s">
+      <c r="D972" t="s">
         <v>2831</v>
       </c>
-      <c r="D972" t="s">
-        <v>2783</v>
-      </c>
       <c r="E972" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F972" t="s">
         <v>21</v>
@@ -58274,16 +58274,16 @@
         <v>720</v>
       </c>
       <c r="J972" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="K972" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="L972" t="s">
         <v>23</v>
       </c>
       <c r="M972" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="N972">
         <v>640</v>
@@ -58292,24 +58292,24 @@
         <v>23</v>
       </c>
       <c r="P972" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q972" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="973" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
+        <v>2833</v>
+      </c>
+      <c r="C973" t="s">
         <v>2834</v>
       </c>
-      <c r="C973" t="s">
-        <v>2835</v>
-      </c>
       <c r="D973" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E973" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F973" t="s">
         <v>21</v>
@@ -58324,16 +58324,16 @@
         <v>720</v>
       </c>
       <c r="J973" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="K973" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="L973" t="s">
         <v>23</v>
       </c>
       <c r="M973" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="N973">
         <v>645</v>
@@ -58342,24 +58342,24 @@
         <v>23</v>
       </c>
       <c r="P973" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q973" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="974" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C974" t="s">
         <v>2839</v>
       </c>
-      <c r="C974" t="s">
-        <v>2840</v>
-      </c>
       <c r="D974" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E974" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F974" t="s">
         <v>21</v>
@@ -58374,16 +58374,16 @@
         <v>720</v>
       </c>
       <c r="J974" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="K974" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="L974" t="s">
         <v>23</v>
       </c>
       <c r="M974" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="N974">
         <v>650</v>
@@ -58392,24 +58392,24 @@
         <v>23</v>
       </c>
       <c r="P974" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q974" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="975" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C975" t="s">
         <v>2841</v>
       </c>
-      <c r="C975" t="s">
-        <v>2842</v>
-      </c>
       <c r="D975" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E975" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F975" t="s">
         <v>21</v>
@@ -58424,16 +58424,16 @@
         <v>720</v>
       </c>
       <c r="J975" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="K975" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="L975" t="s">
         <v>23</v>
       </c>
       <c r="M975" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="N975">
         <v>655</v>
@@ -58442,24 +58442,24 @@
         <v>23</v>
       </c>
       <c r="P975" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q975" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="976" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C976" t="s">
         <v>2843</v>
       </c>
-      <c r="C976" t="s">
-        <v>2844</v>
-      </c>
       <c r="D976" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E976" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F976" t="s">
         <v>21</v>
@@ -58474,16 +58474,16 @@
         <v>720</v>
       </c>
       <c r="J976" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="K976" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="L976" t="s">
         <v>23</v>
       </c>
       <c r="M976" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="N976">
         <v>660</v>
@@ -58492,24 +58492,24 @@
         <v>23</v>
       </c>
       <c r="P976" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q976" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="977" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C977" t="s">
         <v>2845</v>
       </c>
-      <c r="C977" t="s">
-        <v>2846</v>
-      </c>
       <c r="D977" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E977" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F977" t="s">
         <v>21</v>
@@ -58524,16 +58524,16 @@
         <v>720</v>
       </c>
       <c r="J977" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="K977" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="L977" t="s">
         <v>23</v>
       </c>
       <c r="M977" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="N977">
         <v>635</v>
@@ -58542,24 +58542,24 @@
         <v>23</v>
       </c>
       <c r="P977" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q977" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="978" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
+        <v>2846</v>
+      </c>
+      <c r="C978" t="s">
         <v>2847</v>
       </c>
-      <c r="C978" t="s">
-        <v>2848</v>
-      </c>
       <c r="D978" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E978" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F978" t="s">
         <v>21</v>
@@ -58574,16 +58574,16 @@
         <v>720</v>
       </c>
       <c r="J978" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="K978" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="L978" t="s">
         <v>23</v>
       </c>
       <c r="M978" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="N978">
         <v>640</v>
@@ -58592,24 +58592,24 @@
         <v>23</v>
       </c>
       <c r="P978" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q978" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="979" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="979" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="C979" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="D979" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E979" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F979" t="s">
         <v>21</v>
@@ -58624,16 +58624,16 @@
         <v>720</v>
       </c>
       <c r="J979" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="K979" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="L979" t="s">
         <v>23</v>
       </c>
       <c r="M979" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="N979">
         <v>640</v>
@@ -58642,24 +58642,24 @@
         <v>23</v>
       </c>
       <c r="P979" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q979" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="980" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="980" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
+        <v>2849</v>
+      </c>
+      <c r="C980" t="s">
         <v>2850</v>
       </c>
-      <c r="C980" t="s">
-        <v>2851</v>
-      </c>
       <c r="D980" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E980" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F980" t="s">
         <v>21</v>
@@ -58674,16 +58674,16 @@
         <v>720</v>
       </c>
       <c r="J980" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="K980" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="L980" t="s">
         <v>23</v>
       </c>
       <c r="M980" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="N980">
         <v>645</v>
@@ -58692,24 +58692,24 @@
         <v>23</v>
       </c>
       <c r="P980" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q980" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="981" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="981" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
+        <v>2851</v>
+      </c>
+      <c r="C981" t="s">
         <v>2852</v>
       </c>
-      <c r="C981" t="s">
-        <v>2853</v>
-      </c>
       <c r="D981" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E981" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F981" t="s">
         <v>21</v>
@@ -58724,16 +58724,16 @@
         <v>720</v>
       </c>
       <c r="J981" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="K981" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="L981" t="s">
         <v>23</v>
       </c>
       <c r="M981" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="N981">
         <v>650</v>
@@ -58742,24 +58742,24 @@
         <v>23</v>
       </c>
       <c r="P981" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q981" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="982" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="982" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C982" t="s">
         <v>2854</v>
       </c>
-      <c r="C982" t="s">
-        <v>2855</v>
-      </c>
       <c r="D982" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E982" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F982" t="s">
         <v>21</v>
@@ -58774,16 +58774,16 @@
         <v>720</v>
       </c>
       <c r="J982" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="K982" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="L982" t="s">
         <v>23</v>
       </c>
       <c r="M982" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="N982">
         <v>655</v>
@@ -58792,24 +58792,24 @@
         <v>23</v>
       </c>
       <c r="P982" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q982" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="983" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="983" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
+        <v>2855</v>
+      </c>
+      <c r="C983" t="s">
         <v>2856</v>
       </c>
-      <c r="C983" t="s">
-        <v>2857</v>
-      </c>
       <c r="D983" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E983" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F983" t="s">
         <v>21</v>
@@ -58824,16 +58824,16 @@
         <v>720</v>
       </c>
       <c r="J983" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="K983" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="L983" t="s">
         <v>23</v>
       </c>
       <c r="M983" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="N983">
         <v>660</v>
@@ -58842,24 +58842,24 @@
         <v>23</v>
       </c>
       <c r="P983" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q983" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="984" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="984" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
+        <v>2857</v>
+      </c>
+      <c r="C984" t="s">
         <v>2858</v>
       </c>
-      <c r="C984" t="s">
-        <v>2859</v>
-      </c>
       <c r="D984" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E984" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F984" t="s">
         <v>21</v>
@@ -58874,16 +58874,16 @@
         <v>594</v>
       </c>
       <c r="J984" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="K984" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="L984" t="s">
         <v>23</v>
       </c>
       <c r="M984" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="N984">
         <v>725</v>
@@ -58892,24 +58892,24 @@
         <v>23</v>
       </c>
       <c r="P984" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q984" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="985" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="985" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C985" t="s">
         <v>2860</v>
       </c>
-      <c r="C985" t="s">
-        <v>2861</v>
-      </c>
       <c r="D985" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E985" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F985" t="s">
         <v>21</v>
@@ -58924,16 +58924,16 @@
         <v>594</v>
       </c>
       <c r="J985" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="K985" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="L985" t="s">
         <v>23</v>
       </c>
       <c r="M985" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="N985">
         <v>730</v>
@@ -58942,24 +58942,24 @@
         <v>23</v>
       </c>
       <c r="P985" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q985" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="986" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="986" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C986" t="s">
         <v>2862</v>
       </c>
-      <c r="C986" t="s">
-        <v>2863</v>
-      </c>
       <c r="D986" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E986" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F986" t="s">
         <v>21</v>
@@ -58974,16 +58974,16 @@
         <v>594</v>
       </c>
       <c r="J986" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="K986" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="L986" t="s">
         <v>23</v>
       </c>
       <c r="M986" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="N986">
         <v>735</v>
@@ -58992,24 +58992,24 @@
         <v>23</v>
       </c>
       <c r="P986" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q986" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="987" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="987" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
+        <v>2863</v>
+      </c>
+      <c r="C987" t="s">
         <v>2864</v>
       </c>
-      <c r="C987" t="s">
-        <v>2865</v>
-      </c>
       <c r="D987" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E987" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F987" t="s">
         <v>21</v>
@@ -59024,16 +59024,16 @@
         <v>594</v>
       </c>
       <c r="J987" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="K987" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="L987" t="s">
         <v>23</v>
       </c>
       <c r="M987" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="N987">
         <v>740</v>
@@ -59042,24 +59042,24 @@
         <v>23</v>
       </c>
       <c r="P987" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q987" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="988" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="988" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C988" t="s">
         <v>2866</v>
       </c>
-      <c r="C988" t="s">
-        <v>2867</v>
-      </c>
       <c r="D988" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E988" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F988" t="s">
         <v>21</v>
@@ -59074,16 +59074,16 @@
         <v>594</v>
       </c>
       <c r="J988" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="K988" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="L988" t="s">
         <v>23</v>
       </c>
       <c r="M988" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="N988">
         <v>745</v>
@@ -59092,24 +59092,24 @@
         <v>23</v>
       </c>
       <c r="P988" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q988" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="989" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="989" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C989" t="s">
         <v>2868</v>
       </c>
-      <c r="C989" t="s">
-        <v>2869</v>
-      </c>
       <c r="D989" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E989" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F989" t="s">
         <v>21</v>
@@ -59124,16 +59124,16 @@
         <v>594</v>
       </c>
       <c r="J989" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="K989" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="L989" t="s">
         <v>23</v>
       </c>
       <c r="M989" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="N989">
         <v>750</v>
@@ -59142,24 +59142,24 @@
         <v>23</v>
       </c>
       <c r="P989" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q989" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="990" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="990" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C990" t="s">
         <v>2870</v>
       </c>
-      <c r="C990" t="s">
-        <v>2871</v>
-      </c>
       <c r="D990" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E990" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F990" t="s">
         <v>21</v>
@@ -59174,16 +59174,16 @@
         <v>594</v>
       </c>
       <c r="J990" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="K990" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="L990" t="s">
         <v>23</v>
       </c>
       <c r="M990" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="N990">
         <v>720</v>
@@ -59192,24 +59192,24 @@
         <v>23</v>
       </c>
       <c r="P990" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q990" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="991" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="991" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C991" t="s">
         <v>2872</v>
       </c>
-      <c r="C991" t="s">
-        <v>2873</v>
-      </c>
       <c r="D991" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E991" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F991" t="s">
         <v>21</v>
@@ -59224,16 +59224,16 @@
         <v>594</v>
       </c>
       <c r="J991" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="K991" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="L991" t="s">
         <v>23</v>
       </c>
       <c r="M991" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="N991">
         <v>725</v>
@@ -59242,24 +59242,24 @@
         <v>23</v>
       </c>
       <c r="P991" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q991" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="992" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="992" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
+        <v>2873</v>
+      </c>
+      <c r="C992" t="s">
         <v>2874</v>
       </c>
-      <c r="C992" t="s">
-        <v>2875</v>
-      </c>
       <c r="D992" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E992" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F992" t="s">
         <v>21</v>
@@ -59274,16 +59274,16 @@
         <v>594</v>
       </c>
       <c r="J992" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="K992" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="L992" t="s">
         <v>23</v>
       </c>
       <c r="M992" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="N992">
         <v>730</v>
@@ -59292,24 +59292,24 @@
         <v>23</v>
       </c>
       <c r="P992" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q992" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="993" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
+        <v>2875</v>
+      </c>
+      <c r="C993" t="s">
         <v>2876</v>
       </c>
-      <c r="C993" t="s">
-        <v>2877</v>
-      </c>
       <c r="D993" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E993" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F993" t="s">
         <v>21</v>
@@ -59324,16 +59324,16 @@
         <v>594</v>
       </c>
       <c r="J993" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="K993" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="L993" t="s">
         <v>23</v>
       </c>
       <c r="M993" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="N993">
         <v>735</v>
@@ -59342,24 +59342,24 @@
         <v>23</v>
       </c>
       <c r="P993" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q993" t="s">
         <v>2753</v>
       </c>
     </row>
-    <row r="994" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C994" t="s">
         <v>2878</v>
       </c>
-      <c r="C994" t="s">
-        <v>2879</v>
-      </c>
       <c r="D994" t="s">
-        <v>2783</v>
+        <v>2831</v>
       </c>
       <c r="E994" t="s">
-        <v>2838</v>
+        <v>3072</v>
       </c>
       <c r="F994" t="s">
         <v>21</v>
@@ -59374,16 +59374,16 @@
         <v>594</v>
       </c>
       <c r="J994" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="K994" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="L994" t="s">
         <v>23</v>
       </c>
       <c r="M994" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="N994">
         <v>740</v>
@@ -59392,7 +59392,7 @@
         <v>23</v>
       </c>
       <c r="P994" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="Q994" t="s">
         <v>2753</v>
@@ -59400,22 +59400,22 @@
     </row>
     <row r="995" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="B995">
         <v>552977</v>
       </c>
       <c r="C995" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D995" t="s">
         <v>2881</v>
       </c>
-      <c r="D995" t="s">
-        <v>2882</v>
-      </c>
       <c r="E995" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="F995" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="G995" t="s">
         <v>152</v>
@@ -59424,16 +59424,16 @@
         <v>605</v>
       </c>
       <c r="J995" t="s">
+        <v>2882</v>
+      </c>
+      <c r="K995" t="s">
         <v>2883</v>
-      </c>
-      <c r="K995" t="s">
-        <v>2884</v>
       </c>
       <c r="L995" t="s">
         <v>23</v>
       </c>
       <c r="M995" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="N995">
         <v>605</v>
@@ -59442,7 +59442,7 @@
         <v>23</v>
       </c>
       <c r="P995" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Q995" t="s">
         <v>152</v>
@@ -59450,22 +59450,22 @@
     </row>
     <row r="996" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="B996">
         <v>553179</v>
       </c>
       <c r="C996" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="D996" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="E996" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="F996" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="G996" t="s">
         <v>152</v>
@@ -59477,16 +59477,16 @@
         <v>720</v>
       </c>
       <c r="J996" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="K996" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="L996" t="s">
         <v>23</v>
       </c>
       <c r="M996" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="N996">
         <v>615</v>
@@ -59495,7 +59495,7 @@
         <v>23</v>
       </c>
       <c r="P996" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Q996" t="s">
         <v>152</v>
@@ -59503,22 +59503,22 @@
     </row>
     <row r="997" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="B997">
         <v>554190</v>
       </c>
       <c r="C997" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="D997" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="E997" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="F997" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="G997" t="s">
         <v>152</v>
@@ -59530,16 +59530,16 @@
         <v>720</v>
       </c>
       <c r="J997" t="s">
+        <v>2882</v>
+      </c>
+      <c r="K997" t="s">
         <v>2883</v>
-      </c>
-      <c r="K997" t="s">
-        <v>2884</v>
       </c>
       <c r="L997" t="s">
         <v>23</v>
       </c>
       <c r="M997" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="N997">
         <v>620</v>
@@ -59548,7 +59548,7 @@
         <v>23</v>
       </c>
       <c r="P997" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Q997" t="s">
         <v>152</v>
@@ -59556,22 +59556,22 @@
     </row>
     <row r="998" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="B998">
         <v>553177</v>
       </c>
       <c r="C998" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="D998" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="E998" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="F998" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="G998" t="s">
         <v>152</v>
@@ -59583,16 +59583,16 @@
         <v>720</v>
       </c>
       <c r="J998" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="K998" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="L998" t="s">
         <v>23</v>
       </c>
       <c r="M998" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="N998">
         <v>625</v>
@@ -59601,7 +59601,7 @@
         <v>23</v>
       </c>
       <c r="P998" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Q998" t="s">
         <v>152</v>
@@ -59609,19 +59609,19 @@
     </row>
     <row r="999" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
+        <v>2892</v>
+      </c>
+      <c r="C999" t="s">
         <v>2893</v>
       </c>
-      <c r="C999" t="s">
-        <v>2894</v>
-      </c>
       <c r="D999" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="E999" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="F999" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="G999" t="s">
         <v>152</v>
@@ -59633,16 +59633,16 @@
         <v>720</v>
       </c>
       <c r="J999" t="s">
+        <v>2893</v>
+      </c>
+      <c r="K999" t="s">
         <v>2894</v>
-      </c>
-      <c r="K999" t="s">
-        <v>2895</v>
       </c>
       <c r="L999" t="s">
         <v>23</v>
       </c>
       <c r="M999" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N999">
         <v>625</v>
@@ -59651,7 +59651,7 @@
         <v>23</v>
       </c>
       <c r="P999" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Q999" t="s">
         <v>152</v>
@@ -59659,19 +59659,19 @@
     </row>
     <row r="1000" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C1000" t="s">
         <v>2896</v>
       </c>
-      <c r="C1000" t="s">
-        <v>2897</v>
-      </c>
       <c r="D1000" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="E1000" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="F1000" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="G1000" t="s">
         <v>152</v>
@@ -59683,16 +59683,16 @@
         <v>720</v>
       </c>
       <c r="J1000" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="K1000" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="L1000" t="s">
         <v>23</v>
       </c>
       <c r="M1000" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="N1000">
         <v>630</v>
@@ -59701,7 +59701,7 @@
         <v>23</v>
       </c>
       <c r="P1000" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Q1000" t="s">
         <v>152</v>
@@ -59709,19 +59709,19 @@
     </row>
     <row r="1001" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
+        <v>2898</v>
+      </c>
+      <c r="C1001" t="s">
         <v>2899</v>
       </c>
-      <c r="C1001" t="s">
-        <v>2900</v>
-      </c>
       <c r="D1001" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="E1001" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="F1001" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="G1001" t="s">
         <v>152</v>
@@ -59733,16 +59733,16 @@
         <v>720</v>
       </c>
       <c r="J1001" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="K1001" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="L1001" t="s">
         <v>23</v>
       </c>
       <c r="M1001" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N1001">
         <v>620</v>
@@ -59751,7 +59751,7 @@
         <v>23</v>
       </c>
       <c r="P1001" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="Q1001" t="s">
         <v>152</v>
@@ -59759,19 +59759,19 @@
     </row>
     <row r="1002" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1002" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B1002">
         <v>554483</v>
       </c>
       <c r="C1002" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D1002" t="s">
         <v>2903</v>
       </c>
-      <c r="D1002" t="s">
+      <c r="E1002" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1002" t="s">
-        <v>2905</v>
       </c>
       <c r="F1002" t="s">
         <v>21</v>
@@ -59786,16 +59786,16 @@
         <v>936</v>
       </c>
       <c r="J1002" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="K1002" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="L1002" t="s">
         <v>23</v>
       </c>
       <c r="M1002" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="N1002">
         <v>435</v>
@@ -59804,7 +59804,7 @@
         <v>23</v>
       </c>
       <c r="P1002" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1002" t="s">
         <v>22</v>
@@ -59812,19 +59812,19 @@
     </row>
     <row r="1003" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1003" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="B1003">
         <v>554484</v>
       </c>
       <c r="C1003" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="D1003" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1003" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1003" t="s">
-        <v>2905</v>
       </c>
       <c r="F1003" t="s">
         <v>21</v>
@@ -59839,16 +59839,16 @@
         <v>936</v>
       </c>
       <c r="J1003" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="K1003" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="L1003" t="s">
         <v>23</v>
       </c>
       <c r="M1003" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="N1003">
         <v>435</v>
@@ -59857,7 +59857,7 @@
         <v>23</v>
       </c>
       <c r="P1003" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1003" t="s">
         <v>22</v>
@@ -59865,19 +59865,19 @@
     </row>
     <row r="1004" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1004" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="B1004">
         <v>554469</v>
       </c>
       <c r="C1004" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="D1004" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1004" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1004" t="s">
-        <v>2905</v>
       </c>
       <c r="F1004" t="s">
         <v>21</v>
@@ -59892,16 +59892,16 @@
         <v>936</v>
       </c>
       <c r="J1004" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="K1004" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="L1004" t="s">
         <v>23</v>
       </c>
       <c r="M1004" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="N1004">
         <v>440</v>
@@ -59910,7 +59910,7 @@
         <v>23</v>
       </c>
       <c r="P1004" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1004" t="s">
         <v>22</v>
@@ -59918,19 +59918,19 @@
     </row>
     <row r="1005" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1005" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="B1005">
         <v>554478</v>
       </c>
       <c r="C1005" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="D1005" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1005" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1005" t="s">
-        <v>2905</v>
       </c>
       <c r="F1005" t="s">
         <v>21</v>
@@ -59945,16 +59945,16 @@
         <v>936</v>
       </c>
       <c r="J1005" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="K1005" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="L1005" t="s">
         <v>23</v>
       </c>
       <c r="M1005" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="N1005">
         <v>440</v>
@@ -59963,7 +59963,7 @@
         <v>23</v>
       </c>
       <c r="P1005" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1005" t="s">
         <v>22</v>
@@ -59971,19 +59971,19 @@
     </row>
     <row r="1006" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1006" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="B1006">
         <v>554239</v>
       </c>
       <c r="C1006" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="D1006" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1006" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1006" t="s">
-        <v>2905</v>
       </c>
       <c r="F1006" t="s">
         <v>21</v>
@@ -59998,16 +59998,16 @@
         <v>936</v>
       </c>
       <c r="J1006" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="K1006" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="L1006" t="s">
         <v>23</v>
       </c>
       <c r="M1006" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N1006">
         <v>440</v>
@@ -60016,7 +60016,7 @@
         <v>23</v>
       </c>
       <c r="P1006" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1006" t="s">
         <v>22</v>
@@ -60024,16 +60024,16 @@
     </row>
     <row r="1007" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1007" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="C1007" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="D1007" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1007" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1007" t="s">
-        <v>2905</v>
       </c>
       <c r="F1007" t="s">
         <v>21</v>
@@ -60048,16 +60048,16 @@
         <v>936</v>
       </c>
       <c r="J1007" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="K1007" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="L1007" t="s">
         <v>23</v>
       </c>
       <c r="M1007" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="N1007">
         <v>440</v>
@@ -60066,7 +60066,7 @@
         <v>23</v>
       </c>
       <c r="P1007" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1007" t="s">
         <v>22</v>
@@ -60074,16 +60074,16 @@
     </row>
     <row r="1008" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1008" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C1008" t="s">
         <v>2920</v>
       </c>
-      <c r="C1008" t="s">
-        <v>2921</v>
-      </c>
       <c r="D1008" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1008" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1008" t="s">
-        <v>2905</v>
       </c>
       <c r="F1008" t="s">
         <v>21</v>
@@ -60098,16 +60098,16 @@
         <v>936</v>
       </c>
       <c r="J1008" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="K1008" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="L1008" t="s">
         <v>23</v>
       </c>
       <c r="M1008" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="N1008">
         <v>440</v>
@@ -60116,7 +60116,7 @@
         <v>23</v>
       </c>
       <c r="P1008" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1008" t="s">
         <v>22</v>
@@ -60124,19 +60124,19 @@
     </row>
     <row r="1009" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1009" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="B1009">
         <v>554470</v>
       </c>
       <c r="C1009" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="D1009" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1009" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1009" t="s">
-        <v>2905</v>
       </c>
       <c r="F1009" t="s">
         <v>21</v>
@@ -60151,16 +60151,16 @@
         <v>936</v>
       </c>
       <c r="J1009" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="K1009" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="L1009" t="s">
         <v>23</v>
       </c>
       <c r="M1009" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="N1009">
         <v>445</v>
@@ -60169,7 +60169,7 @@
         <v>23</v>
       </c>
       <c r="P1009" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1009" t="s">
         <v>22</v>
@@ -60177,19 +60177,19 @@
     </row>
     <row r="1010" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1010" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="B1010">
         <v>554479</v>
       </c>
       <c r="C1010" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="D1010" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1010" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1010" t="s">
-        <v>2905</v>
       </c>
       <c r="F1010" t="s">
         <v>21</v>
@@ -60204,16 +60204,16 @@
         <v>936</v>
       </c>
       <c r="J1010" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="K1010" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="L1010" t="s">
         <v>23</v>
       </c>
       <c r="M1010" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="N1010">
         <v>445</v>
@@ -60222,7 +60222,7 @@
         <v>23</v>
       </c>
       <c r="P1010" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1010" t="s">
         <v>22</v>
@@ -60230,19 +60230,19 @@
     </row>
     <row r="1011" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1011" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B1011">
         <v>554235</v>
       </c>
       <c r="C1011" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="D1011" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1011" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1011" t="s">
-        <v>2905</v>
       </c>
       <c r="F1011" t="s">
         <v>21</v>
@@ -60257,16 +60257,16 @@
         <v>936</v>
       </c>
       <c r="J1011" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="K1011" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="L1011" t="s">
         <v>23</v>
       </c>
       <c r="M1011" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="N1011">
         <v>445</v>
@@ -60275,7 +60275,7 @@
         <v>23</v>
       </c>
       <c r="P1011" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1011" t="s">
         <v>22</v>
@@ -60283,19 +60283,19 @@
     </row>
     <row r="1012" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1012" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="B1012">
         <v>554240</v>
       </c>
       <c r="C1012" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="D1012" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1012" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1012" t="s">
-        <v>2905</v>
       </c>
       <c r="F1012" t="s">
         <v>21</v>
@@ -60310,16 +60310,16 @@
         <v>936</v>
       </c>
       <c r="J1012" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="K1012" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="L1012" t="s">
         <v>23</v>
       </c>
       <c r="M1012" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="N1012">
         <v>445</v>
@@ -60328,7 +60328,7 @@
         <v>23</v>
       </c>
       <c r="P1012" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1012" t="s">
         <v>22</v>
@@ -60336,19 +60336,19 @@
     </row>
     <row r="1013" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1013" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="B1013">
         <v>554470</v>
       </c>
       <c r="C1013" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="D1013" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1013" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1013" t="s">
-        <v>2905</v>
       </c>
       <c r="F1013" t="s">
         <v>21</v>
@@ -60363,16 +60363,16 @@
         <v>936</v>
       </c>
       <c r="J1013" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="K1013" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="L1013" t="s">
         <v>23</v>
       </c>
       <c r="M1013" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="N1013">
         <v>445</v>
@@ -60381,7 +60381,7 @@
         <v>23</v>
       </c>
       <c r="P1013" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1013" t="s">
         <v>22</v>
@@ -60389,16 +60389,16 @@
     </row>
     <row r="1014" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1014" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="C1014" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="D1014" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1014" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1014" t="s">
-        <v>2905</v>
       </c>
       <c r="F1014" t="s">
         <v>21</v>
@@ -60413,16 +60413,16 @@
         <v>936</v>
       </c>
       <c r="J1014" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="K1014" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="L1014" t="s">
         <v>23</v>
       </c>
       <c r="M1014" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="N1014">
         <v>445</v>
@@ -60431,7 +60431,7 @@
         <v>23</v>
       </c>
       <c r="P1014" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1014" t="s">
         <v>22</v>
@@ -60439,19 +60439,19 @@
     </row>
     <row r="1015" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1015" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="B1015">
         <v>554473</v>
       </c>
       <c r="C1015" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="D1015" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1015" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1015" t="s">
-        <v>2905</v>
       </c>
       <c r="F1015" t="s">
         <v>21</v>
@@ -60466,16 +60466,16 @@
         <v>936</v>
       </c>
       <c r="J1015" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="K1015" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="L1015" t="s">
         <v>23</v>
       </c>
       <c r="M1015" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="N1015">
         <v>450</v>
@@ -60484,7 +60484,7 @@
         <v>23</v>
       </c>
       <c r="P1015" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1015" t="s">
         <v>22</v>
@@ -60492,19 +60492,19 @@
     </row>
     <row r="1016" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1016" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="B1016">
         <v>554480</v>
       </c>
       <c r="C1016" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="D1016" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1016" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1016" t="s">
-        <v>2905</v>
       </c>
       <c r="F1016" t="s">
         <v>21</v>
@@ -60519,16 +60519,16 @@
         <v>936</v>
       </c>
       <c r="J1016" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="K1016" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="L1016" t="s">
         <v>23</v>
       </c>
       <c r="M1016" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="N1016">
         <v>450</v>
@@ -60537,7 +60537,7 @@
         <v>23</v>
       </c>
       <c r="P1016" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1016" t="s">
         <v>22</v>
@@ -60545,19 +60545,19 @@
     </row>
     <row r="1017" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1017" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="B1017">
         <v>554241</v>
       </c>
       <c r="C1017" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="D1017" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1017" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1017" t="s">
-        <v>2905</v>
       </c>
       <c r="F1017" t="s">
         <v>21</v>
@@ -60572,16 +60572,16 @@
         <v>936</v>
       </c>
       <c r="J1017" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="K1017" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="L1017" t="s">
         <v>23</v>
       </c>
       <c r="M1017" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="N1017">
         <v>450</v>
@@ -60590,7 +60590,7 @@
         <v>23</v>
       </c>
       <c r="P1017" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1017" t="s">
         <v>22</v>
@@ -60598,19 +60598,19 @@
     </row>
     <row r="1018" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1018" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="B1018">
         <v>554473</v>
       </c>
       <c r="C1018" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D1018" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1018" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1018" t="s">
-        <v>2905</v>
       </c>
       <c r="F1018" t="s">
         <v>21</v>
@@ -60625,16 +60625,16 @@
         <v>936</v>
       </c>
       <c r="J1018" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="K1018" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="L1018" t="s">
         <v>23</v>
       </c>
       <c r="M1018" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="N1018">
         <v>450</v>
@@ -60643,7 +60643,7 @@
         <v>23</v>
       </c>
       <c r="P1018" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1018" t="s">
         <v>22</v>
@@ -60651,16 +60651,16 @@
     </row>
     <row r="1019" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1019" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="C1019" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D1019" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1019" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1019" t="s">
-        <v>2905</v>
       </c>
       <c r="F1019" t="s">
         <v>21</v>
@@ -60675,16 +60675,16 @@
         <v>936</v>
       </c>
       <c r="J1019" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="K1019" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="L1019" t="s">
         <v>23</v>
       </c>
       <c r="M1019" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="N1019">
         <v>450</v>
@@ -60693,7 +60693,7 @@
         <v>23</v>
       </c>
       <c r="P1019" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1019" t="s">
         <v>22</v>
@@ -60701,16 +60701,16 @@
     </row>
     <row r="1020" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1020" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C1020" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D1020" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1020" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1020" t="s">
-        <v>2905</v>
       </c>
       <c r="F1020" t="s">
         <v>21</v>
@@ -60725,16 +60725,16 @@
         <v>936</v>
       </c>
       <c r="J1020" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="K1020" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="L1020" t="s">
         <v>23</v>
       </c>
       <c r="M1020" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="N1020">
         <v>450</v>
@@ -60743,7 +60743,7 @@
         <v>23</v>
       </c>
       <c r="P1020" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1020" t="s">
         <v>22</v>
@@ -60751,16 +60751,16 @@
     </row>
     <row r="1021" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1021" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C1021" t="s">
         <v>2948</v>
       </c>
-      <c r="C1021" t="s">
-        <v>2949</v>
-      </c>
       <c r="D1021" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1021" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1021" t="s">
-        <v>2905</v>
       </c>
       <c r="F1021" t="s">
         <v>21</v>
@@ -60775,16 +60775,16 @@
         <v>936</v>
       </c>
       <c r="J1021" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="K1021" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="L1021" t="s">
         <v>23</v>
       </c>
       <c r="M1021" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N1021">
         <v>455</v>
@@ -60793,7 +60793,7 @@
         <v>23</v>
       </c>
       <c r="P1021" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1021" t="s">
         <v>22</v>
@@ -60801,16 +60801,16 @@
     </row>
     <row r="1022" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1022" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C1022" t="s">
         <v>2950</v>
       </c>
-      <c r="C1022" t="s">
-        <v>2951</v>
-      </c>
       <c r="D1022" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1022" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1022" t="s">
-        <v>2905</v>
       </c>
       <c r="F1022" t="s">
         <v>21</v>
@@ -60825,16 +60825,16 @@
         <v>936</v>
       </c>
       <c r="J1022" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="K1022" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="L1022" t="s">
         <v>23</v>
       </c>
       <c r="M1022" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="N1022">
         <v>455</v>
@@ -60843,7 +60843,7 @@
         <v>23</v>
       </c>
       <c r="P1022" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1022" t="s">
         <v>22</v>
@@ -60851,19 +60851,19 @@
     </row>
     <row r="1023" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1023" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="B1023">
         <v>554485</v>
       </c>
       <c r="C1023" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1023" t="s">
         <v>2953</v>
-      </c>
-      <c r="D1023" t="s">
-        <v>2904</v>
-      </c>
-      <c r="E1023" t="s">
-        <v>2954</v>
       </c>
       <c r="F1023" t="s">
         <v>21</v>
@@ -60878,16 +60878,16 @@
         <v>864</v>
       </c>
       <c r="J1023" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="K1023" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="L1023" t="s">
         <v>23</v>
       </c>
       <c r="M1023" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="N1023">
         <v>490</v>
@@ -60896,7 +60896,7 @@
         <v>23</v>
       </c>
       <c r="P1023" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1023" t="s">
         <v>139</v>
@@ -60904,19 +60904,19 @@
     </row>
     <row r="1024" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1024" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="B1024">
         <v>554474</v>
       </c>
       <c r="C1024" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="D1024" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1024" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1024" t="s">
         <v>21</v>
@@ -60931,16 +60931,16 @@
         <v>864</v>
       </c>
       <c r="J1024" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="K1024" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="L1024" t="s">
         <v>23</v>
       </c>
       <c r="M1024" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="N1024">
         <v>495</v>
@@ -60949,7 +60949,7 @@
         <v>23</v>
       </c>
       <c r="P1024" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1024" t="s">
         <v>139</v>
@@ -60957,19 +60957,19 @@
     </row>
     <row r="1025" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1025" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B1025">
         <v>554236</v>
       </c>
       <c r="C1025" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="D1025" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1025" t="s">
         <v>2904</v>
-      </c>
-      <c r="E1025" t="s">
-        <v>2905</v>
       </c>
       <c r="F1025" t="s">
         <v>21</v>
@@ -60984,16 +60984,16 @@
         <v>936</v>
       </c>
       <c r="J1025" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="K1025" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="L1025" t="s">
         <v>23</v>
       </c>
       <c r="M1025" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="N1025">
         <v>450</v>
@@ -61002,7 +61002,7 @@
         <v>23</v>
       </c>
       <c r="P1025" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="Q1025" t="s">
         <v>139</v>
@@ -61010,19 +61010,19 @@
     </row>
     <row r="1026" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1026" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="B1026">
         <v>554475</v>
       </c>
       <c r="C1026" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="D1026" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1026" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1026" t="s">
         <v>21</v>
@@ -61037,16 +61037,16 @@
         <v>864</v>
       </c>
       <c r="J1026" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="K1026" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="L1026" t="s">
         <v>23</v>
       </c>
       <c r="M1026" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="N1026">
         <v>500</v>
@@ -61055,7 +61055,7 @@
         <v>23</v>
       </c>
       <c r="P1026" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1026" t="s">
         <v>139</v>
@@ -61063,16 +61063,16 @@
     </row>
     <row r="1027" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1027" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="C1027" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="D1027" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1027" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1027" t="s">
         <v>21</v>
@@ -61087,16 +61087,16 @@
         <v>864</v>
       </c>
       <c r="J1027" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="K1027" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="L1027" t="s">
         <v>23</v>
       </c>
       <c r="M1027" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="N1027">
         <v>500</v>
@@ -61105,7 +61105,7 @@
         <v>23</v>
       </c>
       <c r="P1027" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1027" t="s">
         <v>139</v>
@@ -61113,16 +61113,16 @@
     </row>
     <row r="1028" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1028" t="s">
+        <v>2965</v>
+      </c>
+      <c r="C1028" t="s">
         <v>2966</v>
       </c>
-      <c r="C1028" t="s">
-        <v>2967</v>
-      </c>
       <c r="D1028" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1028" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1028" t="s">
         <v>21</v>
@@ -61137,16 +61137,16 @@
         <v>864</v>
       </c>
       <c r="J1028" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="K1028" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="L1028" t="s">
         <v>23</v>
       </c>
       <c r="M1028" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="N1028">
         <v>500</v>
@@ -61155,7 +61155,7 @@
         <v>23</v>
       </c>
       <c r="P1028" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1028" t="s">
         <v>139</v>
@@ -61163,19 +61163,19 @@
     </row>
     <row r="1029" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1029" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="B1029">
         <v>554268</v>
       </c>
       <c r="C1029" t="s">
+        <v>2969</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1029" t="s">
         <v>2970</v>
-      </c>
-      <c r="D1029" t="s">
-        <v>2904</v>
-      </c>
-      <c r="E1029" t="s">
-        <v>2971</v>
       </c>
       <c r="F1029" t="s">
         <v>21</v>
@@ -61190,16 +61190,16 @@
         <v>864</v>
       </c>
       <c r="J1029" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="K1029" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="L1029" t="s">
         <v>23</v>
       </c>
       <c r="M1029" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="N1029">
         <v>500</v>
@@ -61208,7 +61208,7 @@
         <v>23</v>
       </c>
       <c r="P1029" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="Q1029" t="s">
         <v>139</v>
@@ -61216,19 +61216,19 @@
     </row>
     <row r="1030" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1030" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="B1030">
         <v>554476</v>
       </c>
       <c r="C1030" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="D1030" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1030" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1030" t="s">
         <v>21</v>
@@ -61243,16 +61243,16 @@
         <v>864</v>
       </c>
       <c r="J1030" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="K1030" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="L1030" t="s">
         <v>23</v>
       </c>
       <c r="M1030" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="N1030">
         <v>505</v>
@@ -61261,7 +61261,7 @@
         <v>23</v>
       </c>
       <c r="P1030" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1030" t="s">
         <v>139</v>
@@ -61269,19 +61269,19 @@
     </row>
     <row r="1031" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1031" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="B1031">
         <v>554269</v>
       </c>
       <c r="C1031" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="D1031" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1031" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1031" t="s">
         <v>21</v>
@@ -61296,16 +61296,16 @@
         <v>864</v>
       </c>
       <c r="J1031" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="K1031" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="L1031" t="s">
         <v>23</v>
       </c>
       <c r="M1031" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="N1031">
         <v>505</v>
@@ -61314,7 +61314,7 @@
         <v>23</v>
       </c>
       <c r="P1031" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1031" t="s">
         <v>139</v>
@@ -61322,16 +61322,16 @@
     </row>
     <row r="1032" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1032" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="C1032" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="D1032" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1032" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1032" t="s">
         <v>21</v>
@@ -61346,16 +61346,16 @@
         <v>864</v>
       </c>
       <c r="J1032" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="K1032" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="L1032" t="s">
         <v>23</v>
       </c>
       <c r="M1032" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="N1032">
         <v>505</v>
@@ -61364,7 +61364,7 @@
         <v>23</v>
       </c>
       <c r="P1032" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1032" t="s">
         <v>139</v>
@@ -61372,16 +61372,16 @@
     </row>
     <row r="1033" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1033" t="s">
+        <v>2979</v>
+      </c>
+      <c r="C1033" t="s">
         <v>2980</v>
       </c>
-      <c r="C1033" t="s">
-        <v>2981</v>
-      </c>
       <c r="D1033" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1033" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1033" t="s">
         <v>21</v>
@@ -61396,16 +61396,16 @@
         <v>864</v>
       </c>
       <c r="J1033" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="K1033" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="L1033" t="s">
         <v>23</v>
       </c>
       <c r="M1033" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="N1033">
         <v>505</v>
@@ -61414,7 +61414,7 @@
         <v>23</v>
       </c>
       <c r="P1033" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1033" t="s">
         <v>139</v>
@@ -61422,16 +61422,16 @@
     </row>
     <row r="1034" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1034" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="C1034" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="D1034" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1034" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1034" t="s">
         <v>21</v>
@@ -61446,16 +61446,16 @@
         <v>864</v>
       </c>
       <c r="J1034" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="K1034" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="L1034" t="s">
         <v>23</v>
       </c>
       <c r="M1034" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="N1034">
         <v>505</v>
@@ -61464,7 +61464,7 @@
         <v>23</v>
       </c>
       <c r="P1034" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1034" t="s">
         <v>139</v>
@@ -61472,19 +61472,19 @@
     </row>
     <row r="1035" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1035" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="B1035">
         <v>554477</v>
       </c>
       <c r="C1035" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="D1035" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1035" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F1035" t="s">
         <v>21</v>
@@ -61499,16 +61499,16 @@
         <v>864</v>
       </c>
       <c r="J1035" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="K1035" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="L1035" t="s">
         <v>23</v>
       </c>
       <c r="M1035" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="N1035">
         <v>510</v>
@@ -61517,7 +61517,7 @@
         <v>23</v>
       </c>
       <c r="P1035" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="Q1035" t="s">
         <v>139</v>
@@ -61525,19 +61525,19 @@
     </row>
     <row r="1036" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1036" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="B1036">
         <v>554243</v>
       </c>
       <c r="C1036" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1036" t="s">
         <v>2987</v>
-      </c>
-      <c r="D1036" t="s">
-        <v>2904</v>
-      </c>
-      <c r="E1036" t="s">
-        <v>2988</v>
       </c>
       <c r="F1036" t="s">
         <v>21</v>
@@ -61552,16 +61552,16 @@
         <v>720</v>
       </c>
       <c r="J1036" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="K1036" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="L1036" t="s">
         <v>23</v>
       </c>
       <c r="M1036" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="N1036">
         <v>610</v>
@@ -61570,7 +61570,7 @@
         <v>23</v>
       </c>
       <c r="P1036" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1036" t="s">
         <v>152</v>
@@ -61578,19 +61578,19 @@
     </row>
     <row r="1037" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1037" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="B1037">
         <v>554244</v>
       </c>
       <c r="C1037" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="D1037" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1037" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1037" t="s">
         <v>21</v>
@@ -61605,16 +61605,16 @@
         <v>720</v>
       </c>
       <c r="J1037" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="K1037" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="L1037" t="s">
         <v>23</v>
       </c>
       <c r="M1037" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="N1037">
         <v>615</v>
@@ -61623,7 +61623,7 @@
         <v>23</v>
       </c>
       <c r="P1037" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1037" t="s">
         <v>152</v>
@@ -61631,16 +61631,16 @@
     </row>
     <row r="1038" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="C1038" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="D1038" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1038" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1038" t="s">
         <v>21</v>
@@ -61655,16 +61655,16 @@
         <v>720</v>
       </c>
       <c r="J1038" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="K1038" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="L1038" t="s">
         <v>23</v>
       </c>
       <c r="M1038" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="N1038">
         <v>615</v>
@@ -61673,7 +61673,7 @@
         <v>23</v>
       </c>
       <c r="P1038" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1038" t="s">
         <v>152</v>
@@ -61681,16 +61681,16 @@
     </row>
     <row r="1039" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="C1039" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="D1039" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1039" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1039" t="s">
         <v>21</v>
@@ -61705,16 +61705,16 @@
         <v>720</v>
       </c>
       <c r="J1039" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="K1039" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="L1039" t="s">
         <v>23</v>
       </c>
       <c r="M1039" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="N1039">
         <v>615</v>
@@ -61723,7 +61723,7 @@
         <v>23</v>
       </c>
       <c r="P1039" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1039" t="s">
         <v>152</v>
@@ -61731,19 +61731,19 @@
     </row>
     <row r="1040" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="B1040">
         <v>554245</v>
       </c>
       <c r="C1040" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="D1040" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1040" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1040" t="s">
         <v>21</v>
@@ -61758,16 +61758,16 @@
         <v>720</v>
       </c>
       <c r="J1040" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="K1040" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="L1040" t="s">
         <v>23</v>
       </c>
       <c r="M1040" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="N1040">
         <v>620</v>
@@ -61776,7 +61776,7 @@
         <v>23</v>
       </c>
       <c r="P1040" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1040" t="s">
         <v>152</v>
@@ -61784,16 +61784,16 @@
     </row>
     <row r="1041" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="C1041" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="D1041" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1041" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1041" t="s">
         <v>21</v>
@@ -61808,16 +61808,16 @@
         <v>720</v>
       </c>
       <c r="J1041" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="K1041" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="L1041" t="s">
         <v>23</v>
       </c>
       <c r="M1041" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="N1041">
         <v>620</v>
@@ -61826,7 +61826,7 @@
         <v>23</v>
       </c>
       <c r="P1041" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1041" t="s">
         <v>152</v>
@@ -61834,19 +61834,19 @@
     </row>
     <row r="1042" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1042">
         <v>555363</v>
       </c>
       <c r="C1042" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="D1042" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1042" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1042" t="s">
         <v>21</v>
@@ -61861,16 +61861,16 @@
         <v>720</v>
       </c>
       <c r="J1042" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="K1042" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="L1042" t="s">
         <v>23</v>
       </c>
       <c r="M1042" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="N1042">
         <v>620</v>
@@ -61879,7 +61879,7 @@
         <v>23</v>
       </c>
       <c r="P1042" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1042" t="s">
         <v>152</v>
@@ -61887,16 +61887,16 @@
     </row>
     <row r="1043" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="C1043" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="D1043" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1043" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1043" t="s">
         <v>21</v>
@@ -61911,16 +61911,16 @@
         <v>720</v>
       </c>
       <c r="J1043" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="K1043" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="L1043" t="s">
         <v>23</v>
       </c>
       <c r="M1043" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="N1043">
         <v>620</v>
@@ -61929,7 +61929,7 @@
         <v>23</v>
       </c>
       <c r="P1043" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1043" t="s">
         <v>152</v>
@@ -61937,16 +61937,16 @@
     </row>
     <row r="1044" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C1044" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="D1044" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1044" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1044" t="s">
         <v>21</v>
@@ -61961,16 +61961,16 @@
         <v>720</v>
       </c>
       <c r="J1044" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="K1044" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="L1044" t="s">
         <v>23</v>
       </c>
       <c r="M1044" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="N1044">
         <v>620</v>
@@ -61979,7 +61979,7 @@
         <v>23</v>
       </c>
       <c r="P1044" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1044" t="s">
         <v>152</v>
@@ -61987,16 +61987,16 @@
     </row>
     <row r="1045" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C1045" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="D1045" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1045" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1045" t="s">
         <v>21</v>
@@ -62011,16 +62011,16 @@
         <v>720</v>
       </c>
       <c r="J1045" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="K1045" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="L1045" t="s">
         <v>23</v>
       </c>
       <c r="M1045" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="N1045">
         <v>620</v>
@@ -62029,7 +62029,7 @@
         <v>23</v>
       </c>
       <c r="P1045" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1045" t="s">
         <v>152</v>
@@ -62037,19 +62037,19 @@
     </row>
     <row r="1046" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B1046">
         <v>554246</v>
       </c>
       <c r="C1046" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="D1046" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1046" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1046" t="s">
         <v>21</v>
@@ -62064,16 +62064,16 @@
         <v>720</v>
       </c>
       <c r="J1046" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="K1046" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1046" t="s">
         <v>23</v>
       </c>
       <c r="M1046" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="N1046">
         <v>625</v>
@@ -62082,7 +62082,7 @@
         <v>23</v>
       </c>
       <c r="P1046" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1046" t="s">
         <v>152</v>
@@ -62090,19 +62090,19 @@
     </row>
     <row r="1047" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B1047">
         <v>555364</v>
       </c>
       <c r="C1047" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="D1047" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1047" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1047" t="s">
         <v>21</v>
@@ -62117,16 +62117,16 @@
         <v>720</v>
       </c>
       <c r="J1047" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="K1047" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="L1047" t="s">
         <v>23</v>
       </c>
       <c r="M1047" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="N1047">
         <v>625</v>
@@ -62135,7 +62135,7 @@
         <v>23</v>
       </c>
       <c r="P1047" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1047" t="s">
         <v>152</v>
@@ -62143,16 +62143,16 @@
     </row>
     <row r="1048" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="C1048" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D1048" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1048" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1048" t="s">
         <v>21</v>
@@ -62167,16 +62167,16 @@
         <v>720</v>
       </c>
       <c r="J1048" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="K1048" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1048" t="s">
         <v>23</v>
       </c>
       <c r="M1048" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="N1048">
         <v>625</v>
@@ -62185,7 +62185,7 @@
         <v>23</v>
       </c>
       <c r="P1048" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1048" t="s">
         <v>152</v>
@@ -62193,16 +62193,16 @@
     </row>
     <row r="1049" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="C1049" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D1049" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1049" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1049" t="s">
         <v>21</v>
@@ -62217,16 +62217,16 @@
         <v>720</v>
       </c>
       <c r="J1049" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="K1049" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1049" t="s">
         <v>23</v>
       </c>
       <c r="M1049" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="N1049">
         <v>625</v>
@@ -62235,7 +62235,7 @@
         <v>23</v>
       </c>
       <c r="P1049" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1049" t="s">
         <v>152</v>
@@ -62243,16 +62243,16 @@
     </row>
     <row r="1050" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="C1050" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="D1050" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1050" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1050" t="s">
         <v>21</v>
@@ -62267,16 +62267,16 @@
         <v>720</v>
       </c>
       <c r="J1050" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="K1050" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="L1050" t="s">
         <v>23</v>
       </c>
       <c r="M1050" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="N1050">
         <v>620</v>
@@ -62285,7 +62285,7 @@
         <v>23</v>
       </c>
       <c r="P1050" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1050" t="s">
         <v>152</v>
@@ -62293,16 +62293,16 @@
     </row>
     <row r="1051" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="C1051" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D1051" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1051" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1051" t="s">
         <v>21</v>
@@ -62317,16 +62317,16 @@
         <v>720</v>
       </c>
       <c r="J1051" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="K1051" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1051" t="s">
         <v>23</v>
       </c>
       <c r="M1051" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="N1051">
         <v>625</v>
@@ -62335,7 +62335,7 @@
         <v>23</v>
       </c>
       <c r="P1051" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1051" t="s">
         <v>152</v>
@@ -62343,16 +62343,16 @@
     </row>
     <row r="1052" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C1052" t="s">
         <v>3014</v>
       </c>
-      <c r="C1052" t="s">
-        <v>3015</v>
-      </c>
       <c r="D1052" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1052" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1052" t="s">
         <v>21</v>
@@ -62367,16 +62367,16 @@
         <v>720</v>
       </c>
       <c r="J1052" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="K1052" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="L1052" t="s">
         <v>23</v>
       </c>
       <c r="M1052" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="N1052">
         <v>630</v>
@@ -62385,7 +62385,7 @@
         <v>23</v>
       </c>
       <c r="P1052" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1052" t="s">
         <v>152</v>
@@ -62393,16 +62393,16 @@
     </row>
     <row r="1053" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="C1053" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D1053" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1053" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1053" t="s">
         <v>21</v>
@@ -62417,16 +62417,16 @@
         <v>720</v>
       </c>
       <c r="J1053" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="K1053" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1053" t="s">
         <v>23</v>
       </c>
       <c r="M1053" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="N1053">
         <v>625</v>
@@ -62435,7 +62435,7 @@
         <v>23</v>
       </c>
       <c r="P1053" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1053" t="s">
         <v>152</v>
@@ -62443,16 +62443,16 @@
     </row>
     <row r="1054" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="C1054" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D1054" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1054" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1054" t="s">
         <v>21</v>
@@ -62467,16 +62467,16 @@
         <v>720</v>
       </c>
       <c r="J1054" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="K1054" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1054" t="s">
         <v>23</v>
       </c>
       <c r="M1054" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="N1054">
         <v>625</v>
@@ -62485,7 +62485,7 @@
         <v>23</v>
       </c>
       <c r="P1054" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1054" t="s">
         <v>152</v>
@@ -62493,16 +62493,16 @@
     </row>
     <row r="1055" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="C1055" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D1055" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1055" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1055" t="s">
         <v>21</v>
@@ -62517,16 +62517,16 @@
         <v>720</v>
       </c>
       <c r="J1055" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="K1055" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="L1055" t="s">
         <v>23</v>
       </c>
       <c r="M1055" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="N1055">
         <v>625</v>
@@ -62535,7 +62535,7 @@
         <v>23</v>
       </c>
       <c r="P1055" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1055" t="s">
         <v>152</v>
@@ -62543,16 +62543,16 @@
     </row>
     <row r="1056" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
+        <v>3018</v>
+      </c>
+      <c r="C1056" t="s">
         <v>3019</v>
       </c>
-      <c r="C1056" t="s">
-        <v>3020</v>
-      </c>
       <c r="D1056" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1056" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1056" t="s">
         <v>21</v>
@@ -62567,16 +62567,16 @@
         <v>720</v>
       </c>
       <c r="J1056" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="K1056" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="L1056" t="s">
         <v>23</v>
       </c>
       <c r="M1056" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="N1056">
         <v>630</v>
@@ -62585,7 +62585,7 @@
         <v>23</v>
       </c>
       <c r="P1056" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1056" t="s">
         <v>152</v>
@@ -62593,16 +62593,16 @@
     </row>
     <row r="1057" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C1057" t="s">
         <v>3021</v>
       </c>
-      <c r="C1057" t="s">
-        <v>3022</v>
-      </c>
       <c r="D1057" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1057" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1057" t="s">
         <v>21</v>
@@ -62617,16 +62617,16 @@
         <v>720</v>
       </c>
       <c r="J1057" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="K1057" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="L1057" t="s">
         <v>23</v>
       </c>
       <c r="M1057" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="N1057">
         <v>630</v>
@@ -62635,7 +62635,7 @@
         <v>23</v>
       </c>
       <c r="P1057" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1057" t="s">
         <v>152</v>
@@ -62643,19 +62643,19 @@
     </row>
     <row r="1058" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="B1058">
         <v>555431</v>
       </c>
       <c r="C1058" t="s">
+        <v>3023</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1058" t="s">
         <v>3024</v>
-      </c>
-      <c r="D1058" t="s">
-        <v>2904</v>
-      </c>
-      <c r="E1058" t="s">
-        <v>3025</v>
       </c>
       <c r="F1058" t="s">
         <v>21</v>
@@ -62670,16 +62670,16 @@
         <v>576</v>
       </c>
       <c r="J1058" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="K1058" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="L1058" t="s">
         <v>23</v>
       </c>
       <c r="M1058" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="N1058">
         <v>640</v>
@@ -62688,7 +62688,7 @@
         <v>23</v>
       </c>
       <c r="P1058" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q1058" t="s">
         <v>152</v>
@@ -62696,19 +62696,19 @@
     </row>
     <row r="1059" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B1059">
         <v>554812</v>
       </c>
       <c r="C1059" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="D1059" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1059" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1059" t="s">
         <v>21</v>
@@ -62723,16 +62723,16 @@
         <v>594</v>
       </c>
       <c r="J1059" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="K1059" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="L1059" t="s">
         <v>23</v>
       </c>
       <c r="M1059" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="N1059">
         <v>705</v>
@@ -62741,7 +62741,7 @@
         <v>23</v>
       </c>
       <c r="P1059" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1059" t="s">
         <v>2753</v>
@@ -62749,19 +62749,19 @@
     </row>
     <row r="1060" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="B1060">
         <v>554471</v>
       </c>
       <c r="C1060" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="D1060" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1060" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1060" t="s">
         <v>21</v>
@@ -62776,16 +62776,16 @@
         <v>594</v>
       </c>
       <c r="J1060" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="K1060" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="L1060" t="s">
         <v>23</v>
       </c>
       <c r="M1060" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="N1060">
         <v>710</v>
@@ -62794,7 +62794,7 @@
         <v>23</v>
       </c>
       <c r="P1060" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1060" t="s">
         <v>2753</v>
@@ -62802,19 +62802,19 @@
     </row>
     <row r="1061" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="B1061">
         <v>554481</v>
       </c>
       <c r="C1061" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="D1061" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1061" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1061" t="s">
         <v>21</v>
@@ -62829,16 +62829,16 @@
         <v>594</v>
       </c>
       <c r="J1061" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="K1061" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="L1061" t="s">
         <v>23</v>
       </c>
       <c r="M1061" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="N1061">
         <v>710</v>
@@ -62847,7 +62847,7 @@
         <v>23</v>
       </c>
       <c r="P1061" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1061" t="s">
         <v>2753</v>
@@ -62855,19 +62855,19 @@
     </row>
     <row r="1062" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="B1062">
         <v>554472</v>
       </c>
       <c r="C1062" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="D1062" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1062" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1062" t="s">
         <v>21</v>
@@ -62882,16 +62882,16 @@
         <v>594</v>
       </c>
       <c r="J1062" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="K1062" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="L1062" t="s">
         <v>23</v>
       </c>
       <c r="M1062" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="N1062">
         <v>715</v>
@@ -62900,7 +62900,7 @@
         <v>23</v>
       </c>
       <c r="P1062" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1062" t="s">
         <v>2753</v>
@@ -62908,19 +62908,19 @@
     </row>
     <row r="1063" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="B1063">
         <v>554482</v>
       </c>
       <c r="C1063" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="D1063" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1063" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1063" t="s">
         <v>21</v>
@@ -62935,16 +62935,16 @@
         <v>594</v>
       </c>
       <c r="J1063" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="K1063" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="L1063" t="s">
         <v>23</v>
       </c>
       <c r="M1063" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="N1063">
         <v>715</v>
@@ -62953,7 +62953,7 @@
         <v>23</v>
       </c>
       <c r="P1063" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1063" t="s">
         <v>2753</v>
@@ -62961,16 +62961,16 @@
     </row>
     <row r="1064" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="C1064" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="D1064" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1064" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1064" t="s">
         <v>21</v>
@@ -62985,16 +62985,16 @@
         <v>594</v>
       </c>
       <c r="J1064" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="K1064" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="L1064" t="s">
         <v>23</v>
       </c>
       <c r="M1064" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="N1064">
         <v>715</v>
@@ -63003,7 +63003,7 @@
         <v>23</v>
       </c>
       <c r="P1064" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1064" t="s">
         <v>2753</v>
@@ -63011,16 +63011,16 @@
     </row>
     <row r="1065" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
+        <v>3042</v>
+      </c>
+      <c r="C1065" t="s">
         <v>3043</v>
       </c>
-      <c r="C1065" t="s">
-        <v>3044</v>
-      </c>
       <c r="D1065" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1065" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1065" t="s">
         <v>21</v>
@@ -63035,16 +63035,16 @@
         <v>594</v>
       </c>
       <c r="J1065" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="K1065" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="L1065" t="s">
         <v>23</v>
       </c>
       <c r="M1065" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="N1065">
         <v>720</v>
@@ -63053,7 +63053,7 @@
         <v>23</v>
       </c>
       <c r="P1065" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1065" t="s">
         <v>2753</v>
@@ -63061,16 +63061,16 @@
     </row>
     <row r="1066" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C1066" t="s">
         <v>3045</v>
       </c>
-      <c r="C1066" t="s">
-        <v>3046</v>
-      </c>
       <c r="D1066" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1066" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1066" t="s">
         <v>21</v>
@@ -63085,16 +63085,16 @@
         <v>594</v>
       </c>
       <c r="J1066" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K1066" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="L1066" t="s">
         <v>23</v>
       </c>
       <c r="M1066" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="N1066">
         <v>725</v>
@@ -63103,7 +63103,7 @@
         <v>23</v>
       </c>
       <c r="P1066" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1066" t="s">
         <v>2753</v>
@@ -63111,16 +63111,16 @@
     </row>
     <row r="1067" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C1067" t="s">
         <v>3047</v>
       </c>
-      <c r="C1067" t="s">
-        <v>3048</v>
-      </c>
       <c r="D1067" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1067" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1067" t="s">
         <v>21</v>
@@ -63135,16 +63135,16 @@
         <v>594</v>
       </c>
       <c r="J1067" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="K1067" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="L1067" t="s">
         <v>23</v>
       </c>
       <c r="M1067" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="N1067">
         <v>720</v>
@@ -63153,7 +63153,7 @@
         <v>23</v>
       </c>
       <c r="P1067" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1067" t="s">
         <v>2753</v>
@@ -63161,16 +63161,16 @@
     </row>
     <row r="1068" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="C1068" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="D1068" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1068" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1068" t="s">
         <v>21</v>
@@ -63185,16 +63185,16 @@
         <v>594</v>
       </c>
       <c r="J1068" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="K1068" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="L1068" t="s">
         <v>23</v>
       </c>
       <c r="M1068" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="N1068">
         <v>720</v>
@@ -63203,7 +63203,7 @@
         <v>23</v>
       </c>
       <c r="P1068" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1068" t="s">
         <v>2753</v>
@@ -63211,16 +63211,16 @@
     </row>
     <row r="1069" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="C1069" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="D1069" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1069" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1069" t="s">
         <v>21</v>
@@ -63235,16 +63235,16 @@
         <v>594</v>
       </c>
       <c r="J1069" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K1069" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="L1069" t="s">
         <v>23</v>
       </c>
       <c r="M1069" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="N1069">
         <v>725</v>
@@ -63253,7 +63253,7 @@
         <v>23</v>
       </c>
       <c r="P1069" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1069" t="s">
         <v>2753</v>
@@ -63261,16 +63261,16 @@
     </row>
     <row r="1070" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="C1070" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="D1070" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1070" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1070" t="s">
         <v>21</v>
@@ -63285,16 +63285,16 @@
         <v>594</v>
       </c>
       <c r="J1070" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K1070" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="L1070" t="s">
         <v>23</v>
       </c>
       <c r="M1070" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="N1070">
         <v>725</v>
@@ -63303,7 +63303,7 @@
         <v>23</v>
       </c>
       <c r="P1070" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1070" t="s">
         <v>2753</v>
@@ -63311,16 +63311,16 @@
     </row>
     <row r="1071" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C1071" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="D1071" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1071" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1071" t="s">
         <v>21</v>
@@ -63335,16 +63335,16 @@
         <v>594</v>
       </c>
       <c r="J1071" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K1071" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="L1071" t="s">
         <v>23</v>
       </c>
       <c r="M1071" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="N1071">
         <v>725</v>
@@ -63353,7 +63353,7 @@
         <v>23</v>
       </c>
       <c r="P1071" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1071" t="s">
         <v>2753</v>
@@ -63361,16 +63361,16 @@
     </row>
     <row r="1072" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="C1072" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="D1072" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1072" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1072" t="s">
         <v>21</v>
@@ -63385,16 +63385,16 @@
         <v>594</v>
       </c>
       <c r="J1072" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K1072" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="L1072" t="s">
         <v>23</v>
       </c>
       <c r="M1072" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="N1072">
         <v>725</v>
@@ -63403,7 +63403,7 @@
         <v>23</v>
       </c>
       <c r="P1072" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1072" t="s">
         <v>2753</v>
@@ -63411,16 +63411,16 @@
     </row>
     <row r="1073" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1073" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C1073" t="s">
         <v>3053</v>
       </c>
-      <c r="C1073" t="s">
-        <v>3054</v>
-      </c>
       <c r="D1073" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1073" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1073" t="s">
         <v>21</v>
@@ -63435,16 +63435,16 @@
         <v>594</v>
       </c>
       <c r="J1073" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="K1073" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="L1073" t="s">
         <v>23</v>
       </c>
       <c r="M1073" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="N1073">
         <v>730</v>
@@ -63453,7 +63453,7 @@
         <v>23</v>
       </c>
       <c r="P1073" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1073" t="s">
         <v>2753</v>
@@ -63461,16 +63461,16 @@
     </row>
     <row r="1074" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1074" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C1074" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="D1074" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E1074" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="F1074" t="s">
         <v>21</v>
@@ -63485,16 +63485,16 @@
         <v>594</v>
       </c>
       <c r="J1074" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="K1074" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="L1074" t="s">
         <v>23</v>
       </c>
       <c r="M1074" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="N1074">
         <v>730</v>
@@ -63503,7 +63503,7 @@
         <v>23</v>
       </c>
       <c r="P1074" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="Q1074" t="s">
         <v>2753</v>
